--- a/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
+++ b/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_Evidence Status" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_Item Detail'!$A$3:$W$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_Item Detail'!$A$3:$W$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,7 +66,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -98,11 +98,6 @@
         <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -158,9 +153,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -545,11 +537,10 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BSI.IT.27.C7 Network Device Admin Account Review - Testing walkthrough - testing period 07/01/2025 - 06/30/2026 (v3, updated 10/01/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>BSI.IT.27.C7 Network Device Admin Account Review - Testing walkthrough - testing period 07/01/2025 - 06/30/2026 (final, updated 10/01/2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -557,7 +548,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -756,7 +746,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -767,28 +756,28 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>• Population: quarterly PAM BSI SOX certifications expected in the period = 4 (2025 Q3, 2025 Q4, 2026 Q1, 2026 Q2 cycle). Evidenced in the period: 2025 Q3 (launched 8/1/2025) and 2026 Q1 (launched 4/9/2026). 2025 Q4: not provided. The 2026 Q2 certification was launched 7/22/2026 - after the period end.</t>
+          <t>• Population: PAM BSI SOX certifications performed in the period 07/01/2025 - 06/30/2026. Evidenced: 2025 Q3 (launched 8/1/2025, covers H2 2025) and 2026 Q1 (launched 4/9/2026, covers H1 2026). 2025 Q4: not provided. Only evidence dated within the period is used.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• Samples (RCSA sample size matrix: quarterly control, medium assurance = 2): Sample 1 = 2025 Q3; Sample 2 = 2026 Q1. 2026 Q2 is reported as subsequent-period corroborative evidence only (does not count as a sample).</t>
+          <t>• Samples (RCSA sample size matrix: quarterly control, medium assurance = 2): Sample 1 = 2025 Q3; Sample 2 = 2026 Q1 - one review per half-year of the period.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Scope: the 4 privileged network AD groups in PAM Definition of Privilege section 3.3 - CISCO ISE Administrators, CISCO Network Administrators, ISEAdmin, F5FullAdmin. Coverage: 100% of the memberships in each sample (2025 Q3: 88; 2026 Q1: 61; 2026 Q2 corroborative: 58).</t>
+          <t>• Scope: the 4 privileged network AD groups in PAM Definition of Privilege section 3.3 - CISCO ISE Administrators, CISCO Network Administrators, ISEAdmin, F5FullAdmin. Coverage: 100% of the memberships in each sample (2025 Q3: 88; 2026 Q1: 61).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>• AD account status: 2025 Q3 assessed with the BSI AD extract 11/25/2025 (Q3_2025 workbook: enabled, last logon, expiration); 2026 Q1 / Q2 with the AD extract 05/15/2026 (Q1 2026 workbook: enabled, expiration, last change).</t>
+          <t>• AD account status: 2025 Q3 assessed with the BSI AD extract 11/25/2025 (Q3_2025 workbook: enabled, last logon, expiration); 2026 Q1 with the AD extract 05/15/2026 (Q1 2026 workbook: enabled, expiration, last change).</t>
         </is>
       </c>
     </row>
@@ -820,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -839,7 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -958,17 +946,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>BSI.IT.27.C7 Final 07.2025-06.2026 (evidence received 10/01/2026)</t>
+          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>MD5, size, content (tab 6).</t>
+          <t>MD5, size, content (tab 6); keep only evidence dated in the period.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>13 files in the package + PAM Definition of Privilege.</t>
+          <t>2 in-period evidence workbooks + 3 policies / procedures. Out-of-period files received (2025 Q1, 2025 Q2, 2026 Q2) excluded.</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -993,7 +981,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Certification names / decision dates (Q3_2025, Q1 2026 workbooks; 2026 Q2 CSVs)</t>
+          <t>Certification names / decision dates (Q3_2025, Q1 2026 workbooks)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1003,7 +991,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>In period: 2025 Q3 (launched 8/1/2025, decisions 8/6-8/28/2025) and 2026 Q1 (launched 4/9/2026, decisions 4/10-4/30/2026). 2025 Q4 not provided. 2026 Q2 launched 7/22/2026 (after period end).</t>
+          <t>In period: 2025 Q3 (launched 8/1/2025, decisions 8/6-8/28/2025) and 2026 Q1 (launched 4/9/2026, decisions 4/10-4/30/2026). 2025 Q4 not provided.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1073,7 +1061,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Sample 1 = 2025 Q3; Sample 2 = 2026 Q1. 2026 Q2 tested as corroborative subsequent-period evidence.</t>
+          <t>Sample 1 = 2025 Q3; Sample 2 = 2026 Q1.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1108,7 +1096,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3: 88 (ISE Admins 3, Cisco Net Admins 44, ISEAdmin 36, F5 5). 2026 Q1: 61 (ISE Admins 3, Cisco Net Admins 29, ISEAdmin 24, F5 5). 2026 Q2: 58.</t>
+          <t>2025 Q3: 88 (ISE Admins 3, Cisco Net Admins 44, ISEAdmin 36, F5 5). 2026 Q1: 61 (ISE Admins 3, Cisco Net Admins 29, ISEAdmin 24, F5 5).</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1353,7 +1341,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Reports reconcile to AD / CyberArk. Observations: 2025 Q3 AD extract tags revoked members still present without comment; Q1 2026 export rows repeated 5x; IAMS termination date vs AD expiration inconsistent.</t>
+          <t>Reports reconcile to AD. Observations: 2025 Q3 AD extract tags revoked members still present without comment; Q1 2026 export rows repeated 5x; IAMS termination date vs AD expiration inconsistent.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1373,65 +1361,30 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Corroborate with subsequent period (2026 Q2)</t>
+          <t>Conclude</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2026 Q2 SOX / CyberArk CSVs; AD 05/15/2026</t>
+          <t>Tab 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Same attributes, not counted as a sample.</t>
+          <t>Group fails if any attribute fails; sample fails if any group fails.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026 Q2: 32 memberships fail A5 (same accounts, plus AD expiry 06/01/2026) - confirms the deficiency persisted after the period.</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Corroborative</t>
+          <t>Sample 1 (2025 Q3): FAIL (Cisco Net Admins, ISEAdmin - A5, A6). Sample 2 (2026 Q1): FAIL (Cisco Net Admins, ISEAdmin - A5). ISE Admins and F5FullAdmin pass in both. 2 of 2 samples fail -&gt; control performance Needs Improvement.</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Conclude</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Tab 3</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Group fails if any attribute fails; sample fails if any group fails.</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Sample 1 (2025 Q3): FAIL (Cisco Net Admins, ISEAdmin - A5, A6). Sample 2 (2026 Q1): FAIL (Cisco Net Admins, ISEAdmin - A5). ISE Admins and F5FullAdmin pass in both. 2 of 2 samples fail -&gt; control performance Needs Improvement.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
@@ -1451,7 +1404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1467,11 +1420,10 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Attribute testing table - period 07/01/2025 - 06/30/2026 - Samples 2025 Q3 and 2026 Q1 (+ 2026 Q2 subsequent period, corroborative)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Attribute testing table - period 07/01/2025 - 06/30/2026 - Samples 2025 Q3 and 2026 Q1</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -1901,434 +1853,200 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="180" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>9
-Subsequent period (corroborative)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>2026 Q2
-2026 Q2 PAM BSI SOX Manager Certification (7/22/2026) + 2026 Q2 PAM BSI SOX Entitlement Owner Certification (7/23/2026)</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>CISCO ISE Administrators</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>A2: PASS - 3 memberships certified (1 users / administrators + 2 service accounts); 3 of 3 in AD extract 05/15/2026.
-A3: PASS - managers / owners; no self-review.</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>A4: PASS - 3/3 decisions recorded.
-Approvers: Borges, Dayam (1); Rojo, Ian I (2)
-A5: PASS - approved accounts active (IAMS / AD).</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>A1: Not in period - launched 7/22/2026 (corroborative).
-A6: PASS - # Revocations = 0 (N/A).</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.02 Q2_2026.xlsx tab 1_Cisco ISE Administrators; 2026 Q2 CSVs; AD extract 05/15/2026</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Corroborative - pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="180" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>10
-Subsequent period (corroborative)</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>2026 Q2
-2026 Q2 PAM BSI SOX Manager Certification (7/22/2026) + 2026 Q2 PAM BSI SOX Entitlement Owner Certification (7/23/2026)</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>A2: PASS - 28 memberships certified (23 users / administrators + 5 service accounts); 28 of 28 in AD extract 05/15/2026.
-A3: PASS - managers / owners; no self-review.</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>A4: PASS - 28/28 decisions recorded.
-Approvers: Borges, Dayam (21); Rojo, Ian I (5); Moore, Scott Anthony (1); Pretel, Yohan (1)
-A5: FAIL - 17 of 28 approved: E1 inactive / AD disabled MIA25103, MIA25249, MIA25250, MIA25251, X533062, X688027, X689040, X689379, X690623, X690995; E2 terminated / expired MIA25103, MIA25104, MIA25105, MIA25106, MIA25142, MIA25249, MIA25250, MIA25251, X453396; E3 re-granted after revocation MIA25142, MIA25172, MIA25175, X453396.</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>A1: Not in period - launched 7/22/2026 (corroborative).
-A6: PASS - # Revocations = 0 (N/A).</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.02 Q2_2026.xlsx tab 2_Cisco Network Administrators; 2026 Q2 CSVs; AD extract 05/15/2026</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Corroborative - fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="180" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>11
-Subsequent period (corroborative)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>2026 Q2
-2026 Q2 PAM BSI SOX Manager Certification (7/22/2026) + 2026 Q2 PAM BSI SOX Entitlement Owner Certification (7/23/2026)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>A2: PASS - 23 memberships certified (22 users / administrators + 1 service accounts); 23 of 23 in AD extract 05/15/2026.
-A3: PASS - managers / owners; no self-review.</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>A4: PASS - 23/23 decisions recorded.
-Approvers: Borges, Dayam (19); Moore, Scott Anthony (1); Rojo, Ian I (1); Oliveros, Jose Manuel (1); Pretel, Yohan (1)
-A5: FAIL - 15 of 23 approved: E1 inactive / AD disabled MIA25103, MIA25249, MIA25250, MIA25251, X533062, X688027, X689040, X689379, X690623, X690995; E2 terminated / expired MIA25103, MIA25104, MIA25105, MIA25106, MIA25142, MIA25249, MIA25250, MIA25251, X453396; E3 re-granted after revocation MIA25142, X453396.</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>A1: Not in period - launched 7/22/2026 (corroborative).
-A6: PASS - # Revocations = 0 (N/A).</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.02 Q2_2026.xlsx tab 3_ISEAdmin; 2026 Q2 CSVs; AD extract 05/15/2026</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Corroborative - fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="180" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>12
-Subsequent period (corroborative)</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>2026 Q2
-2026 Q2 PAM BSI SOX Manager Certification (7/22/2026) + 2026 Q2 PAM BSI SOX Entitlement Owner Certification (7/23/2026)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>F5FullAdmin</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>A2: PASS - 4 memberships certified (2 users / administrators + 2 service accounts); 4 of 4 in AD extract 05/15/2026.
-A3: PASS - managers / owners; no self-review.</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>A4: PASS - 4/4 decisions recorded.
-Approvers: Borges, Dayam (2); Rojo, Ian I (2)
-A5: PASS - approved accounts active (IAMS / AD).</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>A1: Not in period - launched 7/22/2026 (corroborative).
-A6: PASS - # Revocations = 0 (N/A).</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.02 Q2_2026.xlsx tab 4_F5FullAdmin; 2026 Q2 CSVs; AD extract 05/15/2026</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Corroborative - pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Attribute conclusion - period 07/01/2025 - 06/30/2026 (Samples 2025 Q3 and 2026 Q1)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Attr.</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Subsequent period (2026 Q2)</t>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Frequency (at least semiannual) &amp; initiation</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Reviews in each half of the period: 2025 Q3 (8/1/2025) and 2026 Q1 (4/9/2026). Observations: 2025 Q4 not evidenced; 8.3 months between launches; Procedure requires quarterly SOX recertification; 2026 Q1 launched after quarter end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Completeness - users / administrators and service accounts</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AD extracts 11/25/2025 and 05/15/2026 reconcile to the certifications; members added after launch were certified in the next review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Reviewer - manager / owner</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Managers / owners in both samples; no self-review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Decision &amp; approvers</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2025 Q3: 88 decisions 8/6-8/28/2025; 2026 Q1: 61 decisions 4/10-4/30/2026.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Frequency (at least semiannual) &amp; initiation</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Pass (observation)</t>
+          <t>Appropriateness of approved access</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Reviews in each half of the period: 2025 Q3 (8/1/2025) and 2026 Q1 (4/9/2026). Observations: 2025 Q4 not evidenced; 8.3 months between launches; Procedure requires quarterly SOX recertification; 2026 Q1 launched after quarter end.</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Launched 7/22/2026</t>
+          <t>2025 Q3: 14 memberships (IAMS-terminated identities, one AD-disabled account). 2026 Q1: 30 memberships (AD-disabled accounts, IAMS-terminated identities, re-granted access).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Completeness - users / administrators and service accounts</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Revocations within SLA</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>AD extracts 11/25/2025 and 05/15/2026 reconcile to the certifications; members added after launch were certified in the next review.</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>AD = certification 58/58</t>
+          <t>2025 Q3 revocations removed within SLA per Netwrix, but 6 memberships were present again in AD on 11/25/2025 (removal not sustained / re-granted without request). 2026 Q1 revocations removed and sustained.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Reviewer - manager / owner</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Information reliability</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Observation</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Managers / owners in both samples; no self-review.</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Decision &amp; approvers</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q3: 88 decisions 8/6-8/28/2025; 2026 Q1: 61 decisions 4/10-4/30/2026.</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Appropriateness of approved access</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q3: 14 memberships (IAMS-terminated identities, one AD-disabled account). 2026 Q1: 30 memberships (AD-disabled accounts, IAMS-terminated identities, re-granted access).</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Fail - 32 memberships</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Revocations within SLA</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q3 revocations removed within SLA per Netwrix, but 6 memberships were present again in AD on 11/25/2025 (removal not sustained / re-granted without request). 2026 Q1 revocations removed and sustained.</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>No revocations</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Information reliability</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
           <t>Reports reconcile; field gaps, duplicated rows, IAMS vs AD inconsistencies; revoked members still in the 2025 Q3 AD extract were not flagged by the 2025 tester.</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Overall (period 07/01/2025 - 06/30/2026): 2 of 2 samples FAIL - CISCO Network Administrators and ISEAdmin (A5 in both samples; A6 in 2025 Q3). Control performance: Needs Improvement. 2026 Q2 (subsequent period) shows the same exceptions, so the deficiency was not remediated after the period.</t>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Overall (period 07/01/2025 - 06/30/2026): 2 of 2 samples FAIL - CISCO Network Administrators and ISEAdmin (A5 in both samples; A6 in 2025 Q3). Control performance: Needs Improvement.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2341,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W210"/>
+  <dimension ref="A1:W152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2372,11 +2090,10 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Every tested membership - 2025 Q3 (88), 2026 Q1 (61), 2026 Q2 corroborative (58) - IAMS and AD status, result per attribute</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Every tested membership - 2025 Q3 (88), 2026 Q1 (61) - IAMS and AD status, result per attribute</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2182,7 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Prior decision</t>
+          <t>Prior in-period decision (2025 Q3)</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -2804,7 +2521,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
@@ -3482,7 +3199,7 @@
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
@@ -3595,7 +3312,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -3708,7 +3425,7 @@
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
@@ -3821,7 +3538,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
@@ -3934,7 +3651,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
@@ -4047,7 +3764,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
@@ -4160,7 +3877,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
@@ -4273,7 +3990,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
@@ -4386,7 +4103,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
@@ -4499,7 +4216,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
@@ -4725,7 +4442,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
@@ -4838,7 +4555,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
@@ -4951,7 +4668,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
@@ -5064,7 +4781,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
@@ -5177,7 +4894,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
@@ -5290,7 +5007,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
@@ -5403,7 +5120,7 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
@@ -5516,7 +5233,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
@@ -5629,7 +5346,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
@@ -5742,7 +5459,7 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
@@ -5855,7 +5572,7 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
@@ -5968,7 +5685,7 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
@@ -6081,7 +5798,7 @@
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
@@ -6194,7 +5911,7 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S36" s="6" t="inlineStr">
@@ -6307,7 +6024,7 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
@@ -6420,7 +6137,7 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
@@ -6533,7 +6250,7 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -6646,7 +6363,7 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S40" s="6" t="inlineStr">
@@ -6759,7 +6476,7 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
@@ -6872,7 +6589,7 @@
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S42" s="6" t="inlineStr">
@@ -6985,7 +6702,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S43" s="6" t="inlineStr">
@@ -7098,7 +6815,7 @@
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S44" s="6" t="inlineStr">
@@ -7211,7 +6928,7 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S45" s="6" t="inlineStr">
@@ -8002,7 +7719,7 @@
       </c>
       <c r="R52" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S52" s="6" t="inlineStr">
@@ -8115,7 +7832,7 @@
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S53" s="6" t="inlineStr">
@@ -8228,7 +7945,7 @@
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S54" s="6" t="inlineStr">
@@ -8341,7 +8058,7 @@
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S55" s="6" t="inlineStr">
@@ -8454,7 +8171,7 @@
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S56" s="6" t="inlineStr">
@@ -8567,7 +8284,7 @@
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S57" s="6" t="inlineStr">
@@ -8680,7 +8397,7 @@
       </c>
       <c r="R58" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
@@ -8793,7 +8510,7 @@
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S59" s="6" t="inlineStr">
@@ -8906,7 +8623,7 @@
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S60" s="6" t="inlineStr">
@@ -9019,7 +8736,7 @@
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S61" s="6" t="inlineStr">
@@ -9132,7 +8849,7 @@
       </c>
       <c r="R62" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S62" s="6" t="inlineStr">
@@ -9245,7 +8962,7 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S63" s="6" t="inlineStr">
@@ -9358,7 +9075,7 @@
       </c>
       <c r="R64" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S64" s="6" t="inlineStr">
@@ -9471,7 +9188,7 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S65" s="6" t="inlineStr">
@@ -9584,7 +9301,7 @@
       </c>
       <c r="R66" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S66" s="6" t="inlineStr">
@@ -9697,7 +9414,7 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S67" s="6" t="inlineStr">
@@ -9810,7 +9527,7 @@
       </c>
       <c r="R68" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S68" s="6" t="inlineStr">
@@ -9923,7 +9640,7 @@
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S69" s="6" t="inlineStr">
@@ -10036,7 +9753,7 @@
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S70" s="6" t="inlineStr">
@@ -10149,7 +9866,7 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S71" s="6" t="inlineStr">
@@ -10262,7 +9979,7 @@
       </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S72" s="6" t="inlineStr">
@@ -10375,7 +10092,7 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S73" s="6" t="inlineStr">
@@ -10488,7 +10205,7 @@
       </c>
       <c r="R74" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S74" s="6" t="inlineStr">
@@ -10601,7 +10318,7 @@
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S75" s="6" t="inlineStr">
@@ -10714,7 +10431,7 @@
       </c>
       <c r="R76" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S76" s="6" t="inlineStr">
@@ -10827,7 +10544,7 @@
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S77" s="6" t="inlineStr">
@@ -10940,7 +10657,7 @@
       </c>
       <c r="R78" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S78" s="6" t="inlineStr">
@@ -11053,7 +10770,7 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S79" s="6" t="inlineStr">
@@ -11166,7 +10883,7 @@
       </c>
       <c r="R80" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S80" s="6" t="inlineStr">
@@ -11279,7 +10996,7 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S81" s="6" t="inlineStr">
@@ -12183,7 +11900,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S89" s="6" t="inlineStr">
@@ -12296,7 +12013,7 @@
       </c>
       <c r="R90" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S90" s="6" t="inlineStr">
@@ -12409,7 +12126,7 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S91" s="6" t="inlineStr">
@@ -19331,6678 +19048,8 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>CISCO ISE Administrators</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM (owner Borges, Dayam)</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>7/27/26, 12:45 PM</t>
-        </is>
-      </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M153" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N153" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O153" s="4" t="inlineStr">
-        <is>
-          <t>06/19/2025</t>
-        </is>
-      </c>
-      <c r="P153" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q153" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R153" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S153" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T153" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U153" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V153" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W153" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>CISCO ISE Administrators</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>MIASOLAR</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>MIASOLAR (owner Rojo, Ian I)</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I154" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>7/28/26, 9:29 AM</t>
-        </is>
-      </c>
-      <c r="K154" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M154" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N154" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O154" s="4" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
-        </is>
-      </c>
-      <c r="P154" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R154" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S154" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T154" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U154" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V154" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W154" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>CISCO ISE Administrators</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>MIAPERR</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>Perez Urquiza, Rober</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K155" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M155" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N155" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O155" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P155" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q155" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R155" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S155" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T155" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U155" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V155" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W155" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM (owner Borges, Dayam)</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>7/27/26, 12:45 PM</t>
-        </is>
-      </c>
-      <c r="K156" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M156" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N156" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O156" s="4" t="inlineStr">
-        <is>
-          <t>06/19/2025</t>
-        </is>
-      </c>
-      <c r="P156" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R156" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S156" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T156" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U156" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V156" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W156" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>MIAALGOSEC</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>MIAALGOSEC (owner Heredia, Evelio Alejandro)</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>8/6/26, 6:16 PM</t>
-        </is>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M157" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N157" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O157" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P157" s="4" t="n">
-        <v>827</v>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R157" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S157" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T157" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U157" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V157" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W157" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>MIACPRIME</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>MIACPRIME (owner Rojo, Ian I)</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>7/28/26, 9:29 AM</t>
-        </is>
-      </c>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M158" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>05/14/2026</t>
-        </is>
-      </c>
-      <c r="P158" s="4" t="n">
-        <v>820</v>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R158" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S158" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T158" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U158" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V158" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W158" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>MIAQUALYS</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>MIAQUALYS (owner Borges, Dayam)</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I159" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>7/27/26, 12:45 PM</t>
-        </is>
-      </c>
-      <c r="K159" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M159" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N159" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O159" s="4" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="P159" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q159" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R159" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S159" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T159" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U159" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V159" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W159" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>MIASOLAR</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>MIASOLAR (owner Rojo, Ian I)</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>7/28/26, 9:29 AM</t>
-        </is>
-      </c>
-      <c r="K160" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M160" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N160" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O160" s="4" t="inlineStr">
-        <is>
-          <t>05/12/2026</t>
-        </is>
-      </c>
-      <c r="P160" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q160" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R160" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S160" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T160" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U160" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V160" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W160" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>MIA19047</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>Figueroa, Juan</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M161" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N161" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O161" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P161" s="4" t="n">
-        <v>847</v>
-      </c>
-      <c r="Q161" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R161" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S161" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T161" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U161" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V161" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W161" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>MIA20037</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>Grenier, Adrian</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>Moore, Scott Anthony</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K162" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M162" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N162" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O162" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P162" s="4" t="n">
-        <v>912</v>
-      </c>
-      <c r="Q162" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R162" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S162" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T162" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U162" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V162" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W162" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>MIA24991</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>Leiva, Felix</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M163" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N163" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O163" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P163" s="4" t="n">
-        <v>1543</v>
-      </c>
-      <c r="Q163" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R163" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S163" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T163" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U163" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V163" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W163" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>MIA25103</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>Ramirez Gonzalez, Ivan</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M164" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N164" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O164" s="4" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
-        </is>
-      </c>
-      <c r="P164" s="4" t="n">
-        <v>1614</v>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R164" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S164" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T164" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U164" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V164" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W164" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>MIA25104</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>Paez Venegas, Jefferson</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I165" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K165" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M165" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N165" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O165" s="4" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="P165" s="4" t="n">
-        <v>1612</v>
-      </c>
-      <c r="Q165" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R165" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S165" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T165" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U165" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V165" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W165" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>MIA25105</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>Serrano Aguirre, David</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K166" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M166" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N166" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O166" s="4" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="P166" s="4" t="n">
-        <v>1613</v>
-      </c>
-      <c r="Q166" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R166" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S166" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T166" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U166" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V166" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W166" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>MIA25106</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>Vazquez Arias, Maiko</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M167" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N167" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O167" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P167" s="4" t="n">
-        <v>1611</v>
-      </c>
-      <c r="Q167" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R167" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S167" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T167" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U167" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V167" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W167" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>MIA25142</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>Nieves Nieves, Miguel</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I168" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K168" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M168" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N168" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O168" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P168" s="4" t="n">
-        <v>1636</v>
-      </c>
-      <c r="Q168" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R168" s="4" t="inlineStr">
-        <is>
-          <t>Revoked</t>
-        </is>
-      </c>
-      <c r="S168" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T168" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U168" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision; E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
-        </is>
-      </c>
-      <c r="V168" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W168" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>MIA25172</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>Hernandez Ruiz, Juan</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="H169" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N169" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O169" s="4" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="P169" s="4" t="n">
-        <v>1655</v>
-      </c>
-      <c r="Q169" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R169" s="4" t="inlineStr">
-        <is>
-          <t>Revoked</t>
-        </is>
-      </c>
-      <c r="S169" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T169" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U169" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
-        </is>
-      </c>
-      <c r="V169" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W169" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>MIA25175</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>Hernandez Acevedo, Carlos</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K170" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M170" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N170" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O170" s="4" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
-        </is>
-      </c>
-      <c r="P170" s="4" t="n">
-        <v>1656</v>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R170" s="4" t="inlineStr">
-        <is>
-          <t>Revoked</t>
-        </is>
-      </c>
-      <c r="S170" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T170" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U170" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
-        </is>
-      </c>
-      <c r="V170" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W170" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>MIA25249</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>Harris, Richard</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M171" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O171" s="4" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
-        </is>
-      </c>
-      <c r="P171" s="4" t="n">
-        <v>1799</v>
-      </c>
-      <c r="Q171" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R171" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S171" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T171" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U171" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V171" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W171" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>MIA25250</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>Ackley, Kevin</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I172" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M172" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N172" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O172" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P172" s="4" t="n">
-        <v>1798</v>
-      </c>
-      <c r="Q172" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R172" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S172" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T172" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U172" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V172" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W172" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>MIA25251</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>Rimal, Ashish</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K173" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M173" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N173" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O173" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P173" s="4" t="n">
-        <v>1797</v>
-      </c>
-      <c r="Q173" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R173" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S173" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T173" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U173" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V173" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W173" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>MIAPERR</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr">
-        <is>
-          <t>Perez Urquiza, Rober</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J174" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K174" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M174" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N174" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O174" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P174" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q174" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R174" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S174" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T174" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U174" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V174" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W174" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>X453396</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>Perez Peralta, Juan Fernando</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J175" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K175" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N175" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O175" s="4" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="P175" s="4" t="n">
-        <v>1847</v>
-      </c>
-      <c r="Q175" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R175" s="4" t="inlineStr">
-        <is>
-          <t>Revoked</t>
-        </is>
-      </c>
-      <c r="S175" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T175" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U175" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 AD account expired 06/01/2026 before the decision; E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
-        </is>
-      </c>
-      <c r="V175" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W175" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>X458741</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr">
-        <is>
-          <t>Flores, Leonardo</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>Pretel, Yohan</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J176" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M176" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N176" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O176" s="4" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="P176" s="4" t="n">
-        <v>1060</v>
-      </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R176" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S176" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T176" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U176" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V176" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W176" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>X533062</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>Armattoe, Michael</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J177" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M177" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N177" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O177" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P177" s="4" t="n">
-        <v>2045</v>
-      </c>
-      <c r="Q177" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R177" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S177" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T177" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U177" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V177" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W177" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>X688027</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>Guzman, Yazir</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K178" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M178" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N178" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O178" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P178" s="4" t="n">
-        <v>2201</v>
-      </c>
-      <c r="Q178" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R178" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S178" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T178" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U178" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V178" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W178" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>X689040</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>Vazquez Hernandez, Jesus</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K179" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M179" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N179" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O179" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P179" s="4" t="n">
-        <v>2206</v>
-      </c>
-      <c r="Q179" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R179" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S179" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T179" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U179" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V179" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W179" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>X689379</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>Martinez Cervantes, Pamela</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K180" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M180" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N180" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O180" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P180" s="4" t="n">
-        <v>2203</v>
-      </c>
-      <c r="Q180" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R180" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S180" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T180" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U180" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V180" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W180" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>X690623</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>Jimenez, Carlos</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G181" s="4" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H181" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K181" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M181" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N181" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O181" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P181" s="4" t="n">
-        <v>2202</v>
-      </c>
-      <c r="Q181" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R181" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S181" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T181" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U181" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V181" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W181" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>X690995</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>Martinez, Jose Antonio</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K182" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M182" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N182" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O182" s="4" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="P182" s="4" t="n">
-        <v>2204</v>
-      </c>
-      <c r="Q182" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R182" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S182" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T182" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U182" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS)</t>
-        </is>
-      </c>
-      <c r="V182" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W182" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>X842395</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>Fernandez Yanez, Xochitl</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F183" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H183" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I183" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J183" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K183" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M183" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N183" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O183" s="4" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="P183" s="4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="Q183" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R183" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S183" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T183" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U183" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V183" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W183" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM (owner Borges, Dayam)</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G184" s="4" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I184" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>7/27/26, 12:45 PM</t>
-        </is>
-      </c>
-      <c r="K184" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M184" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N184" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O184" s="4" t="inlineStr">
-        <is>
-          <t>06/19/2025</t>
-        </is>
-      </c>
-      <c r="P184" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q184" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R184" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S184" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T184" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U184" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V184" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W184" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>MIA20037</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>Grenier, Adrian</t>
-        </is>
-      </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F185" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G185" s="4" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H185" s="4" t="inlineStr">
-        <is>
-          <t>Moore, Scott Anthony</t>
-        </is>
-      </c>
-      <c r="I185" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J185" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K185" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L185" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M185" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N185" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O185" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P185" s="4" t="n">
-        <v>912</v>
-      </c>
-      <c r="Q185" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R185" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S185" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T185" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U185" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V185" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W185" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>MIA25103</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>Ramirez Gonzalez, Ivan</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K186" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L186" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M186" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N186" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O186" s="4" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
-        </is>
-      </c>
-      <c r="P186" s="4" t="n">
-        <v>1614</v>
-      </c>
-      <c r="Q186" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R186" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S186" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T186" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U186" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V186" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W186" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>MIA25104</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>Paez Venegas, Jefferson</t>
-        </is>
-      </c>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F187" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="H187" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J187" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K187" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L187" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M187" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N187" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O187" s="4" t="inlineStr">
-        <is>
-          <t>04/28/2026</t>
-        </is>
-      </c>
-      <c r="P187" s="4" t="n">
-        <v>1612</v>
-      </c>
-      <c r="Q187" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R187" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S187" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T187" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U187" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V187" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W187" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>MIA25105</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>Serrano Aguirre, David</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F188" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H188" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J188" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K188" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L188" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M188" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N188" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O188" s="4" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="P188" s="4" t="n">
-        <v>1613</v>
-      </c>
-      <c r="Q188" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R188" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S188" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T188" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U188" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V188" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W188" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>MIA25106</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>Vazquez Arias, Maiko</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="H189" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J189" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K189" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M189" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N189" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O189" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P189" s="4" t="n">
-        <v>1611</v>
-      </c>
-      <c r="Q189" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R189" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S189" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T189" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U189" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V189" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W189" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>MIA25142</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr">
-        <is>
-          <t>Nieves Nieves, Miguel</t>
-        </is>
-      </c>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F190" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H190" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J190" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K190" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M190" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N190" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O190" s="4" t="inlineStr">
-        <is>
-          <t>05/13/2026</t>
-        </is>
-      </c>
-      <c r="P190" s="4" t="n">
-        <v>1636</v>
-      </c>
-      <c r="Q190" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R190" s="4" t="inlineStr">
-        <is>
-          <t>Revoked</t>
-        </is>
-      </c>
-      <c r="S190" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T190" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U190" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision; E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
-        </is>
-      </c>
-      <c r="V190" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W190" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>MIA25172</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>Hernandez Ruiz, Juan</t>
-        </is>
-      </c>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="H191" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J191" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K191" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M191" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N191" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O191" s="4" t="inlineStr">
-        <is>
-          <t>05/07/2026</t>
-        </is>
-      </c>
-      <c r="P191" s="4" t="n">
-        <v>1655</v>
-      </c>
-      <c r="Q191" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R191" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S191" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T191" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U191" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V191" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W191" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>MIA25175</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>Hernandez Acevedo, Carlos</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F192" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H192" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I192" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J192" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K192" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L192" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M192" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N192" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O192" s="4" t="inlineStr">
-        <is>
-          <t>04/27/2026</t>
-        </is>
-      </c>
-      <c r="P192" s="4" t="n">
-        <v>1656</v>
-      </c>
-      <c r="Q192" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R192" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S192" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T192" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U192" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V192" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W192" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>MIA25249</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>Harris, Richard</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="H193" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J193" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K193" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L193" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M193" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N193" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O193" s="4" t="inlineStr">
-        <is>
-          <t>04/02/2026</t>
-        </is>
-      </c>
-      <c r="P193" s="4" t="n">
-        <v>1799</v>
-      </c>
-      <c r="Q193" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R193" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S193" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T193" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U193" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V193" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W193" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>MIA25250</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr">
-        <is>
-          <t>Ackley, Kevin</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J194" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K194" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M194" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N194" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O194" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P194" s="4" t="n">
-        <v>1798</v>
-      </c>
-      <c r="Q194" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R194" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S194" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T194" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U194" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V194" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W194" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>MIA25251</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>Rimal, Ashish</t>
-        </is>
-      </c>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="H195" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J195" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K195" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L195" s="4" t="inlineStr">
-        <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="M195" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N195" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O195" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P195" s="4" t="n">
-        <v>1797</v>
-      </c>
-      <c r="Q195" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R195" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S195" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T195" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U195" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024; E2 AD account expired 06/01/2026 before the decision</t>
-        </is>
-      </c>
-      <c r="V195" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W195" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>MIAPERR</t>
-        </is>
-      </c>
-      <c r="D196" s="4" t="inlineStr">
-        <is>
-          <t>Perez Urquiza, Rober</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K196" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M196" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N196" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O196" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P196" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q196" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R196" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S196" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T196" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U196" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V196" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W196" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>MIAROJO</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F197" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G197" s="4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H197" s="4" t="inlineStr">
-        <is>
-          <t>Oliveros, Jose Manuel</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J197" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K197" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L197" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M197" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N197" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O197" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P197" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q197" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R197" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S197" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T197" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U197" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V197" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W197" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>X453396</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>Perez Peralta, Juan Fernando</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J198" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K198" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M198" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N198" s="4" t="inlineStr">
-        <is>
-          <t>06/01/2026</t>
-        </is>
-      </c>
-      <c r="O198" s="4" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
-        </is>
-      </c>
-      <c r="P198" s="4" t="n">
-        <v>1847</v>
-      </c>
-      <c r="Q198" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R198" s="4" t="inlineStr">
-        <is>
-          <t>Revoked</t>
-        </is>
-      </c>
-      <c r="S198" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T198" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U198" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E2 AD account expired 06/01/2026 before the decision; E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
-        </is>
-      </c>
-      <c r="V198" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W198" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>X458741</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>Flores, Leonardo</t>
-        </is>
-      </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr">
-        <is>
-          <t>Pretel, Yohan</t>
-        </is>
-      </c>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J199" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K199" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L199" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M199" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N199" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O199" s="4" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="P199" s="4" t="n">
-        <v>1060</v>
-      </c>
-      <c r="Q199" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R199" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S199" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T199" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U199" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V199" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W199" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>X533062</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr">
-        <is>
-          <t>Armattoe, Michael</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F200" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I200" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J200" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K200" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M200" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N200" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O200" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P200" s="4" t="n">
-        <v>2045</v>
-      </c>
-      <c r="Q200" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R200" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S200" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T200" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U200" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V200" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W200" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>X688027</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>Guzman, Yazir</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="H201" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J201" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K201" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L201" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M201" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N201" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O201" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P201" s="4" t="n">
-        <v>2201</v>
-      </c>
-      <c r="Q201" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R201" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S201" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T201" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U201" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V201" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W201" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>X689040</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="inlineStr">
-        <is>
-          <t>Vazquez Hernandez, Jesus</t>
-        </is>
-      </c>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F202" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G202" s="4" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J202" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K202" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L202" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M202" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N202" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O202" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P202" s="4" t="n">
-        <v>2206</v>
-      </c>
-      <c r="Q202" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R202" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S202" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T202" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U202" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V202" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W202" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>X689379</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>Martinez Cervantes, Pamela</t>
-        </is>
-      </c>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="H203" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I203" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J203" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K203" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L203" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M203" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N203" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O203" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P203" s="4" t="n">
-        <v>2203</v>
-      </c>
-      <c r="Q203" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R203" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S203" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T203" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U203" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V203" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W203" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>X690623</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr">
-        <is>
-          <t>Jimenez, Carlos</t>
-        </is>
-      </c>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G204" s="4" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="H204" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J204" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K204" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L204" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M204" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N204" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O204" s="4" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="P204" s="4" t="n">
-        <v>2202</v>
-      </c>
-      <c r="Q204" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R204" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S204" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T204" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U204" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS); E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
-        </is>
-      </c>
-      <c r="V204" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W204" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>X690995</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Martinez, Jose Antonio</t>
-        </is>
-      </c>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="H205" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I205" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J205" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K205" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="L205" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M205" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N205" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O205" s="4" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="P205" s="4" t="n">
-        <v>2204</v>
-      </c>
-      <c r="Q205" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R205" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S205" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T205" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U205" s="8" t="inlineStr">
-        <is>
-          <t>Fail - E1 Identity Inactive = True (IAMS)</t>
-        </is>
-      </c>
-      <c r="V205" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W205" s="8" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>ISEAdmin</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>X842395</t>
-        </is>
-      </c>
-      <c r="D206" s="4" t="inlineStr">
-        <is>
-          <t>Fernandez Yanez, Xochitl</t>
-        </is>
-      </c>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G206" s="4" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I206" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J206" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K206" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L206" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M206" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N206" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2027</t>
-        </is>
-      </c>
-      <c r="O206" s="4" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="P206" s="4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R206" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S206" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T206" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U206" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V206" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W206" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>F5FullAdmin</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>ITOPS_W_ADM (owner Borges, Dayam)</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I207" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J207" s="4" t="inlineStr">
-        <is>
-          <t>7/27/26, 12:45 PM</t>
-        </is>
-      </c>
-      <c r="K207" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M207" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N207" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O207" s="4" t="inlineStr">
-        <is>
-          <t>06/19/2025</t>
-        </is>
-      </c>
-      <c r="P207" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q207" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R207" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S207" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T207" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U207" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V207" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W207" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>F5FullAdmin</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>MIAQUALYS</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>MIAQUALYS (owner Borges, Dayam)</t>
-        </is>
-      </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>Non person (service account)</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner cert (Daily Active.csv)</t>
-        </is>
-      </c>
-      <c r="G208" s="4" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H208" s="4" t="inlineStr">
-        <is>
-          <t>Borges, Dayam</t>
-        </is>
-      </c>
-      <c r="I208" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J208" s="4" t="inlineStr">
-        <is>
-          <t>7/27/26, 12:45 PM</t>
-        </is>
-      </c>
-      <c r="K208" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L208" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M208" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N208" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O208" s="4" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="P208" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R208" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S208" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T208" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U208" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V208" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W208" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>F5FullAdmin</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>MIA24991</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>Leiva, Felix</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="H209" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J209" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K209" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L209" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M209" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N209" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O209" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P209" s="4" t="n">
-        <v>1543</v>
-      </c>
-      <c r="Q209" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R209" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S209" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T209" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U209" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V209" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W209" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 (Subsequent period)</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>F5FullAdmin</t>
-        </is>
-      </c>
-      <c r="C210" s="4" t="inlineStr">
-        <is>
-          <t>MIAPERR</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr">
-        <is>
-          <t>Perez Urquiza, Rober</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="F210" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager cert (Validation1.csv)</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="H210" s="4" t="inlineStr">
-        <is>
-          <t>Rojo, Ian I</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J210" s="4" t="inlineStr">
-        <is>
-          <t>not in export</t>
-        </is>
-      </c>
-      <c r="K210" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L210" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M210" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N210" s="4" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-      <c r="O210" s="4" t="inlineStr">
-        <is>
-          <t>05/15/2026</t>
-        </is>
-      </c>
-      <c r="P210" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q210" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R210" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="S210" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T210" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U210" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V210" s="4" t="inlineStr">
-        <is>
-          <t>N/A - Approved</t>
-        </is>
-      </c>
-      <c r="W210" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:W210"/>
+  <autoFilter ref="A3:W152"/>
   <mergeCells count="1">
     <mergeCell ref="A1:W1"/>
   </mergeCells>
@@ -26016,7 +19063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -26032,11 +19079,10 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Exceptions - evidence trail per account (A5 / A6) - period 07/01/2025 - 06/30/2026, plus 2026 Q2 corroboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Exceptions - evidence trail per account (A5 / A6) - period 07/01/2025 - 06/30/2026</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -26102,7 +19148,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -26116,10 +19162,7 @@
           <t>2025 Q3: E1 AD account disabled (AD 11/25/2025), last logon 10/15/2023 - no use since before the review
 2025 Q3: E2 IAMS Termination Date 12/31/2024
 2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -26151,7 +19194,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -26163,9 +19206,7 @@
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: E2 IAMS Termination Date 12/31/2024
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -26197,7 +19238,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -26209,9 +19250,7 @@
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: E2 IAMS Termination Date 12/31/2024
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -26243,7 +19282,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -26255,9 +19294,7 @@
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: E2 IAMS Termination Date 12/31/2024
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -26289,7 +19326,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -26302,10 +19339,7 @@
         <is>
           <t>2025 Q3: FAIL - removal not sustained: revoked 8/28/2025, removed 09/02/2025 (Netwrix) but member again in AD 11/25/2025 (E3)
 2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q1: E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
+2026 Q1: E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -26337,7 +19371,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -26349,8 +19383,7 @@
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: FAIL - removal not sustained: revoked 8/28/2025, removed 09/02/2025 (Netwrix) but member again in AD 11/25/2025 (E3)
-2026 Q1: E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request
-2026 Q2: E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
+2026 Q1: E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -26382,7 +19415,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -26394,8 +19427,7 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: FAIL - removal not sustained: revoked 8/28/2025, removed 09/08/2025 (Netwrix) but member again in AD 11/25/2025 (E3)
-2026 Q1: E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request
-2026 Q2: E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
+2026 Q1: E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -26427,7 +19459,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -26440,10 +19472,7 @@
         <is>
           <t>2025 Q3: E2 IAMS Termination Date 12/31/2024
 2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -26475,7 +19504,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -26488,10 +19517,7 @@
         <is>
           <t>2025 Q3: E2 IAMS Termination Date 12/31/2024
 2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -26523,7 +19549,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -26536,10 +19562,7 @@
         <is>
           <t>2025 Q3: E2 IAMS Termination Date 12/31/2024
 2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q1: E2 IAMS Termination Date 12/31/2024
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E2 IAMS Termination Date 12/31/2024</t>
+2026 Q1: E2 IAMS Termination Date 12/31/2024</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -26551,7 +19574,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>E2, E3</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -26571,7 +19594,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2025 Q3, 2026 Q1, 2026 Q2</t>
+          <t>2025 Q3, 2026 Q1</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -26583,9 +19606,7 @@
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: FAIL - removal not sustained: revoked 8/28/2025, removed 09/08/2025 (Netwrix) but member again in AD 11/25/2025 (E3)
-2026 Q1: E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request
-2026 Q2: E2 AD account expired 06/01/2026 before the decision
-2026 Q2: E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
+2026 Q1: E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -26617,7 +19638,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1, 2026 Q2</t>
+          <t>2026 Q1</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -26627,8 +19648,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
+          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -26660,7 +19680,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1, 2026 Q2</t>
+          <t>2026 Q1</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -26670,9 +19690,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 Identity Inactive = True (IAMS)</t>
+          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -26704,7 +19722,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1, 2026 Q2</t>
+          <t>2026 Q1</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -26714,9 +19732,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 Identity Inactive = True (IAMS)</t>
+          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -26748,7 +19764,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1, 2026 Q2</t>
+          <t>2026 Q1</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -26758,9 +19774,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 Identity Inactive = True (IAMS)</t>
+          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -26792,7 +19806,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1, 2026 Q2</t>
+          <t>2026 Q1</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -26802,9 +19816,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision
-2026 Q2: E1 Identity Inactive = True (IAMS)</t>
+          <t>2026 Q1: E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -26813,59 +19825,16 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>X690995</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Martinez, Jose Antonio</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>CISCO Network Administrators; ISEAdmin</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>AD extract 05/15/2026: enabled True, exp. 01/01/2027, 05/04/2026</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2: E1 Identity Inactive = True (IAMS)</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Approved / revoked by Borges, Dayam (2025 Q3 8/28/2025; 2026 Q1 4/30/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Totals: 17 accounts. In period - 2025 Q3: 20 memberships (A5 14, A6 6); 2026 Q1: 30 memberships. Subsequent 2026 Q2: 32 memberships. E1 = IAMS inactive / AD disabled; E2 = IAMS terminated / AD expired; E3 = revoked access present again / re-granted without approved request.</t>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Totals: 16 accounts. 2025 Q3: 20 memberships (A5 14, A6 6); 2026 Q1: 30 memberships (A5 30). E1 = IAMS inactive / AD disabled; E2 = IAMS terminated / AD expired; E3 = revoked access present again / re-granted without approved request.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26878,7 +19847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -26896,7 +19865,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -26942,7 +19910,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>v11.0 (07/28/2026)</t>
+          <t>Standard v11.0 (07/28/2026)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -26974,7 +19942,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>v2.0 (04/22/2026)</t>
+          <t>Procedure v2.0 (04/22/2026)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -26994,392 +19962,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.02 Q3_2025.xlsx</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 02 Evidence 07.2025-06.2026</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>2025 Q3 - SAMPLE 1</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>3743 KB</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>2025 Q3 SOX Manager / Owner certification (launched 8/1/2025), AD extract 11/25/2025, Netwrix revocation logs</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>9df232d76e15d4e56a5f55da1d84aa4a</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>BSI.IT.27.C7.03 PAM Definition of Privilege.pdf</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 01 Policies and Procedures</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Policy v10.0 (3/11/2025)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>233 KB</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Section 3.3 Network Administration (scope)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>6e2cace9acada78339c9320ff92d9c7a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>BSI.IT.27.C7.02 Q3_2025.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 02 Evidence 07.2025-06.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2025 Q3 - SAMPLE 1 (H2 2025)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>3743 KB</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2025 Q3 SOX Manager / Owner certification (launched 8/1/2025, decisions 8/6-8/28/2025), AD extract 11/25/2025, Netwrix revocation logs 9/2-9/8/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>9df232d76e15d4e56a5f55da1d84aa4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>BSI.IT.27.C7.02 Q1 2026 Cert.xlsx</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 02 Evidence 07.2025-06.2026</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>2026 Q1 - SAMPLE 2</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>2026 Q1 - SAMPLE 2 (H1 2026)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>3063 KB</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2026 Q1 SOX Manager / Owner certification (launched 4/9/2026), AD extract 05/15/2026, Netwrix revocation logs</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2026 Q1 SOX Manager / Owner certification (launched 4/9/2026, decisions 4/10-4/30/2026), AD extract 05/15/2026, Netwrix revocation logs 4/16-4/24/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>8d338a2151c9c28eff23af70e6583695</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 PAM BSI SOX Manager Certification - Validation1.csv</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 03 Subsequent Period - Corroborative</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 - subsequent</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>78 KB</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Manager certification (launched 7/22/2026) - corroborative</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>51324252a99574321cc2f4722ad31bf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 PAM BSI SOX Entitlement Owner Certification - Daily Active.csv</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 03 Subsequent Period - Corroborative</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 - subsequent</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>182 KB</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 SOX Owner certification - corroborative</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>830c0819b2f629babf0e526644009451</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 PAM BSI CyberArk Manager Certification - Daily.csv</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 03 Subsequent Period - Corroborative</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 - subsequent</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>356 KB</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>IAMS identity status; reconciliation</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>9fb3dc4c9bc876618547eb3c9e83d827</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 PAM BSI CyberArk Entitlement Owner Certification - Daily Active.csv</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 03 Subsequent Period - Corroborative</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>2026 Q2 - subsequent</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>2067 KB</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Owner reconciliation</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>c256c8bb2d1028159e62837bde3f84d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.02 Q1_2025 Cert.xlsx</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 New Testing Evidences-10-1--2026 (received package - prior period, not relied on; not in final folder)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q1 - prior period</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>1647 KB</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Frequency history</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2e26f890d99a687013414a4c47db73b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2025Q2PamBsiSoxDecision-Manager.csv</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 New Testing Evidences-10-1--2026 (received package - prior period, not relied on; not in final folder)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q2 - prior period</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Frequency history; 2025 Q2 revocations</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>4a38977e6db5783eeac1251598cf3471</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2025Q2PamBsiSoxDecision-Owner.csv</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 New Testing Evidences-10-1--2026 (received package - prior period, not relied on; not in final folder)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q2 - prior period</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>176 KB</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Frequency history</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>c83782cb317107fb916bfcf3f74fa289</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>2025Q2PamBsiCyberarkDecision-Manager.csv</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 New Testing Evidences-10-1--2026 (received package - prior period, not relied on; not in final folder)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q2 - prior period</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>427 KB</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Reconciliation</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>4cc02f5848f037be8c842772409bb974</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2025Q2PamBsiCyberarkDecision-Owner.csv</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 New Testing Evidences-10-1--2026 (received package - prior period, not relied on; not in final folder)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q2 - prior period</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>2312 KB</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Reconciliation</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>a4f29621896a653b9b9b73dfa0d2236a</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7.03 PAM Definition of Privilege.pdf</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 01 Policies and Procedures</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>v10.0 (3/11/2025)</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>233 KB</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Section 3.3 Network Administration (scope)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>6e2cace9acada78339c9320ff92d9c7a</t>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Only evidence within the testing period 07/01/2025 - 06/30/2026 is used. Files received 10/01/2026 that fall outside the period (2025 Q1, 2025 Q2, 2026 Q2 certifications) are not relied on and are not in the final folder.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27410,7 +20098,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -27529,7 +20216,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>HR / vendor status at the review dates (8/28/2025, 4/30/2026) for X688027, X689040, X689379, X690623, X690995, X533062, MIA25103</t>
+          <t>HR / vendor status at the review dates (8/28/2025, 4/30/2026) for X688027, X689040, X689379, X690623, X533062, MIA25103</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -27798,9 +20485,8 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Essential to close the testing: #1 (2025 Q4) and #2 (management response). #3-#5 decide whether any exception can be cleared.</t>
         </is>

--- a/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
+++ b/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Control statement; PAM Recertification Procedure v2.0 (04/22/2026) sec. 2 &amp; 8.1 C7; IAM Std v11.0 SUS.IAMS.4.2.5.6, 4.2.5.9, 4.2.5.19</t>
+          <t>Control statement; PAM Recertification Procedure v2.0 (04/22/2026) sec. 2 &amp; 8.1 C7; IAM Std v10.0 (09/29/2025) SUS.IAMS.4.2.5.6, 4.2.5.9, 4.2.5.19</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>IAM Standard (CUSO) v11.0 07.28.26 sec. 4.2.5; PAM Recertification Procedure (BSI) v2.0 04.22.26</t>
+          <t>IAM Standard v10.0 (approved 09/29/2025) sec. 4.2.5; PAM Recertification Procedure (BSI) v2.0 (approved 04/22/2026)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>BSI.IT.27.C7.01.Identity and Access Management Standard (CUSO) 07.28.26.pdf</t>
+          <t>BSI.IT.27.C7.01 Identity and Access Management Standard v10.0 09.29.2025.pdf</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -19910,22 +19910,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Standard v11.0 (07/28/2026)</t>
+          <t>Standard v10.0 (approved 09/29/2025) - in effect in the period</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>777 KB</t>
+          <t>647 KB</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Criteria SUS.IAMS.4.2.5.x</t>
+          <t>Criteria SUS.IAMS.4.2.5.x (4.2.5.19 privileged access at least semi-annually; 4.2.5.21 revocation within 30 business days)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>35484fd4951ac6439d9e4aee56437c38</t>
+          <t>bc6cbef4c58ffd183348884d02a16cee</t>
         </is>
       </c>
     </row>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Control C7, quarterly SOX recertification, revocation steps 9-10</t>
+          <t>Control C7, quarterly SOX recertification, revocation steps 9-10 (v1.0 of 04/22/2025 applied before 04/22/2026)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -20079,7 +20079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -20452,41 +20452,76 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Criteria</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>IAM Standard v9.0 (in effect 07/01-09/28/2025) and PAM Recertification Procedure v1.0 (04/22/2025, in effect until 04/21/2026) - the versions in force at the 2025 Q3 review</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Policy administration</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Confirms criteria at the 2025 Q3 review date; v10.0 / v2.0 requirements used are unchanged in v11.0 (SUS.IAMS.4.2.5.x).</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Decision whether Network_support (PAM Definition 3.2) is in scope</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>InfoSec / control owner</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Scope observation.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Essential to close the testing: #1 (2025 Q4) and #2 (management response). #3-#5 decide whether any exception can be cleared.</t>
         </is>
@@ -20494,8 +20529,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
+++ b/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Exceptions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_Sources" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_Evidence Status" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_Procedure Coverage" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4_Item Detail'!$A$3:$W$152</definedName>
@@ -20079,7 +20080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -20487,41 +20488,76 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Steps 6-7</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ServiceNow revocation tickets for the 2025 Q3 / 2026 Q1 revocations and any exception / issue record (escalation, owner, due date, tracking to closure) for the A5 / A6 exceptions</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>PAM / IAM; control owner</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Needed to test exception handling and escalation (procedure steps 6-7); without it steps 6-7 remain Fail (not evidenced).</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Decision whether Network_support (PAM Definition 3.2) is in scope</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>InfoSec / control owner</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Scope observation.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Essential to close the testing: #1 (2025 Q4) and #2 (management response). #3-#5 decide whether any exception can be cleared.</t>
         </is>
@@ -20529,8 +20565,342 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage of the 9-step test procedure - period 07/01/2025 - 06/30/2026 - samples 2025 Q3 and 2026 Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Test procedure step</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Work performed and result</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Where documented</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Obtain Evidence</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Campaign documentation, certification records, reviewer decisions, account populations, revocation populations, campaign completion records, evidence of removals by PAM/IAM.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Obtained: 2025 Q3 and 2026 Q1 SailPoint Manager / Owner certification exports (decisions, decision maker, sign-off dates), AD extracts 11/25/2025 and 05/15/2026, Netwrix removal logs, IAM Standard v10.0, PAM Recertification Procedure v2.0, PAM Definition of Privilege v10.0. Not provided: 2025 Q4 certification, ServiceNow revocation tickets, 2026 Q1 campaign completion screenshot.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Tabs 6, 7; 02 Evidence; 01 Policies</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Validate Report Completeness and Accuracy</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Reconcile the certified population to the authoritative source; investigate discrepancies.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Certified memberships reconciled to the BSI AD extracts (authoritative source). 2025 Q3: differences explained (revoked and removed; N584407 left after review; X842395, MIA25172 / MIA25175 ISEAdmin added after launch and certified in 2026 Q1). 2026 Q1: 58/58 AD members certified; 3 extra = revoked and removed. Report observations: Q1 export rows repeated 5x (de-duplicated), IAMS termination vs AD expiration inconsistent.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Step 8; Sample of 1 Exhibit C1; tab 4</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Validate Population and Scope</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>All in-scope administrator, user and service accounts included; none excluded.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Scope = 4 privileged network AD groups (PAM Definition of Privilege sec. 3.3). 88 memberships in 2025 Q3 and 61 in 2026 Q1, person and service accounts, 100% tested; no in-scope account excluded. Observation: Network_support (sec. 3.2) not in scope - management to confirm.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Steps 1, 7; tab 3</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Verify Control Execution</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Sample per RCSA methodology incl. revocations; InfoSec initiated the campaign; authorized manager / owner; decisions documented and completed; revocations identified through the review.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Sample: 2 quarterly campaigns (medium assurance), 100% of memberships including all 36 revocation decisions. Initiation: campaigns launched in SailPoint by the PAM / IAM team (8/1 and 8/4/2025; 4/9/2026) per Procedure sec. 8 steps 1-7. Reviewer: line managers / owners, no self-review. Decisions: 88/88 and 61/61 with sign-off. Revocations identified: 33 in 2025 Q3, 3 in 2026 Q1. BUT the reviewers approved access that should have been revoked (A5: 2025 Q3 14, 2026 Q1 30 memberships).</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Steps 6, 9-12; tab 3; tab 5</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Fail (A5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Validate Control Results</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Revoked access removed by PAM/IAM within SLA after the review and consistent with the decision.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2025 Q3: 33 revoked 8/28/2025, removed 9/2-9/8/2025 (Netwrix) - within 30 business days and matching the decisions; 6 memberships (X453396 x2, MIA25142 x2, MIA25172, MIA25175) were members again on 11/25/2025 - removal not sustained. 2026 Q1: N596764 x2 removed 4/24/2026, MIAYPER 4/17/2026 - within SLA, absent from AD 05/15/2026.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Step 13; Sample of 1 Exhibits B4 / B5</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Fail (A6 - 2025 Q3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Verify Exception Handling</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Where revocations were late, reviews incomplete or reviewer authorization missing, verify the exception was documented and managed per procedure.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>No reviews were incomplete and no reviewer authorization issues were found. The exceptions found by testing (approved terminated / disabled accounts; 6 revoked memberships present again in AD) were not identified, documented or managed by the PAM / IAM team - no exception record, ticket or comment exists in the evidence (the 2025 Q3 AD extract shows the revoked members without comment).</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Tab 5; Evidence Status #2, #12</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Fail (not evidenced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Verify Escalation and Remediation</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Exceptions escalated; remediation documented, assigned and tracked to resolution.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>No escalation, remediation plan, owner or tracking was provided for the exceptions; the same accounts were approved again in the next review (2025 Q3 -&gt; 2026 Q1), showing they were not remediated within the period. Management response and issue / action driver required.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Tab 5; Evidence Status #2, #12</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Fail (not evidenced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Assess Risk Mitigation</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Does the review identify inappropriate access and drive timely revocation?</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Partially. The review is initiated, complete and performed by the right reviewers, and revocations that were raised were removed on time. However it did not identify terminated / disabled accounts in Cisco Network Administrators and ISEAdmin in either review, and removals were not sustained, so the risk of inappropriate privileged network access is not fully mitigated.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Tab 3 conclusion; WP2 CPA</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Fail - Needs Improvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Summarize Testing Coverage</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Coverage of completeness / accuracy, scope, initiation, reviewer authorization, execution, revocation decisions, timeliness, exception management, escalation, risk mitigation.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Completeness &amp; accuracy: Pass (obs.). Scope: Pass (obs.). Initiation / frequency: Pass (obs. - 2025 Q4 missing). Reviewer authorization: Pass. Certification execution: Pass. Revocation decisions / appropriateness: Fail. Timeliness of removal: Pass within SLA, Fail on persistence (2025 Q3). Exception management: Fail (not evidenced). Escalation: Fail (not evidenced). Risk mitigation: Fail. Overall: 2 of 2 samples Fail - Needs Improvement.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>This tab; WP2 C39</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Fail - Needs Improvement</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
+++ b/BSI.IT.27.C7 Network Device Admin Accoun/BSI.IT.27.C7 Final 07.2025-06.2026/00 Final Workpaper/BSI.IT.27.C7.05 Testing Walkthrough - Step by Step.xlsx
@@ -52,6 +52,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FFFF0000"/>
       <sz val="10"/>
     </font>
@@ -61,13 +66,8 @@
       <color rgb="FF9C0006"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,12 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -143,22 +148,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -810,26 +824,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Step-by-step procedure - period 07/01/2025 - 06/30/2026 - source, logic, result</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Step-by-step test procedure (9 steps) - period 07/01/2025 - 06/30/2026 - source, logic, result</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Step</t>
@@ -867,525 +881,888 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>STEP 1 - OBTAIN EVIDENCE</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Tabs 6, 7; 02 Evidence; 01 Policies</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Campaign documentation, certification records, reviewer decisions, account populations, revocation populations, campaign completion records, evidence of removals by PAM/IAM.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Obtained: 2025 Q3 and 2026 Q1 SailPoint Manager / Owner certification exports (decisions, decision maker, sign-off dates), AD extracts 11/25/2025 and 05/15/2026, Netwrix removal logs, IAM Standard v10.0, PAM Recertification Procedure v2.0, PAM Definition of Privilege v10.0. Not provided: 2025 Q4 certification, ServiceNow revocation tickets, 2026 Q1 campaign completion screenshot.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Identify criteria</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>IAM Standard v10.0 (approved 09/29/2025) sec. 4.2.5; PAM Recertification Procedure (BSI) v2.0 (approved 04/22/2026)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Frequency, reviewer, revocation, terminated users.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Procedure 8.1 C7 = this control; SOX privileged recertification quarterly (sec. 2); revocation for rejects / terminated users and PAM verification (sec. 8 steps 9-10); 30 business days (IAM 4.2.5.21).</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Inventory evidence</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MD5, size, content (tab 6); keep only evidence dated in the period.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2 in-period evidence workbooks + 3 policies / procedures. Out-of-period files received (2025 Q1, 2025 Q2, 2026 Q2) excluded.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Define population for the period 07/01/2025 - 06/30/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Certification names / decision dates (Q3_2025, Q1 2026 workbooks)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>List quarterly certifications launched in the period.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>In period: 2025 Q3 (launched 8/1/2025, decisions 8/6-8/28/2025) and 2026 Q1 (launched 4/9/2026, decisions 4/10-4/30/2026). 2025 Q4 not provided.</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>STEP 2 - VALIDATE REPORT COMPLETENESS AND ACCURACY</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Step 8; Sample of 1 Exhibit C1; tab 4</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Reconcile the certified population to the authoritative source; investigate discrepancies.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Certified memberships reconciled to the BSI AD extracts (authoritative source). 2025 Q3: differences explained (revoked and removed; N584407 left after review; X842395, MIA25172 / MIA25175 ISEAdmin added after launch and certified in 2026 Q1). 2026 Q1: 58/58 AD members certified; 3 extra = revoked and removed. Report observations: Q1 export rows repeated 5x (de-duplicated), IAMS termination vs AD expiration inconsistent.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Reconcile to Active Directory</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>AD extract 11/25/2025 (Q3_2025 tabs 1-4) and 05/15/2026 (Q1 2026 tabs 1-4)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AD members vs certified memberships.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2025 Q3: all approved members in AD except N584407 (removed after review); AD members not certified = X842395 (added 8/30/2025) and MIA25172 / MIA25175 ISEAdmin (added 9/10/2025) - added after the campaign launch, certified in 2026 Q1. 2026 Q1: all 58 AD members certified; 3 revoked memberships removed.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Check report reliability</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>All sources</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Fields and reconciliations.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Reports reconcile to AD. Observations: 2025 Q3 AD extract tags revoked members still present without comment; Q1 2026 export rows repeated 5x; IAMS termination date vs AD expiration inconsistent.</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>STEP 3 - VALIDATE POPULATION AND SCOPE</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Steps 1, 7; tab 3</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>All in-scope administrator, user and service accounts included; none excluded.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Scope = 4 privileged network AD groups (PAM Definition of Privilege sec. 3.3). 88 memberships in 2025 Q3 and 61 in 2026 Q1, person and service accounts, 100% tested; no in-scope account excluded. Observation: Network_support (sec. 3.2) not in scope - management to confirm.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Pass (observation)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Identify in-scope privileged network groups</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>BSI.IT.27.C7.03 PAM Definition of Privilege.pdf - sec. 3.3</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Read section 3.3 and the document history (v10.0, 3/11/2025).</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Scope = 4 groups. Observation: section 3.2 also lists Network_support.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Identify criteria</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>IAM Standard v10.0 (approved 09/29/2025) sec. 4.2.5; PAM Recertification Procedure (BSI) v2.0 (approved 04/22/2026)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Frequency, reviewer, revocation, terminated users.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Procedure 8.1 C7 = this control; SOX privileged recertification quarterly (sec. 2); revocation for rejects / terminated users and PAM verification (sec. 8 steps 9-10); 30 business days (IAM 4.2.5.21).</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Inventory evidence</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>MD5, size, content (tab 6); keep only evidence dated in the period.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2 in-period evidence workbooks + 3 policies / procedures. Out-of-period files received (2025 Q1, 2025 Q2, 2026 Q2) excluded.</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Define population for the period 07/01/2025 - 06/30/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Certification names / decision dates (Q3_2025, Q1 2026 workbooks)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>List quarterly certifications launched in the period.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>In period: 2025 Q3 (launched 8/1/2025, decisions 8/6-8/28/2025) and 2026 Q1 (launched 4/9/2026, decisions 4/10-4/30/2026). 2025 Q4 not provided.</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Extract memberships of the 4 groups</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Entitlement Value field</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Parse account and group; filter the 4 groups; Q1 2026 duplicates removed.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2025 Q3: 88 (ISE Admins 3, Cisco Net Admins 44, ISEAdmin 36, F5 5). 2026 Q1: 61 (ISE Admins 3, Cisco Net Admins 29, ISEAdmin 24, F5 5).</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>STEP 4 - VERIFY CONTROL EXECUTION</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Steps 6, 9-12; tab 3; tab 5</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Sample per RCSA methodology incl. revocations; InfoSec initiated the campaign; authorized manager / owner; decisions documented and completed; revocations identified through the review.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Sample: 2 quarterly campaigns (medium assurance), 100% of memberships including all 36 revocation decisions. Initiation: campaigns launched in SailPoint by the PAM / IAM team (8/1 and 8/4/2025; 4/9/2026) per Procedure sec. 8 steps 1-7. Reviewer: line managers / owners, no self-review. Decisions: 88/88 and 61/61 with sign-off. Revocations identified: 33 in 2025 Q3, 3 in 2026 Q1. BUT the reviewers approved access that should have been revoked (A5: 2025 Q3 14, 2026 Q1 30 memberships).</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Fail (A5)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Assess frequency</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Step 4</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>At least one review in each half-year; interval between reviews; Procedure quarterly.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>H2 2025: 2025 Q3 review (Aug 2025). H1 2026: 2026 Q1 review (Apr 2026) -&gt; semiannual requirement met per half-year. Observations: 8.3 months between launches (8/1/2025 -&gt; 4/9/2026); 2025 Q4 quarterly review not evidenced (Procedure requires quarterly SOX).</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Pass (observation)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Assess frequency</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Step 4</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>At least one review in each half-year; interval between reviews; Procedure quarterly.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>H2 2025: 2025 Q3 review (Aug 2025). H1 2026: 2026 Q1 review (Apr 2026) -&gt; semiannual requirement met per half-year. Observations: 8.3 months between launches (8/1/2025 -&gt; 4/9/2026); 2025 Q4 quarterly review not evidenced (Procedure requires quarterly SOX).</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Pass (observation)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Select samples</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Q3_2025.xlsx tab 2 (manager rows 2332-2618, owner rows 2621-2960); Q1 2026 Cert.xlsx tab 2 (rows 2470-3495, 3498-4851)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Two in-period certifications (medium assurance).</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Sample 1 = 2025 Q3; Sample 2 = 2026 Q1.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Sample</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Extract memberships of the 4 groups</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Entitlement Value field</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Parse account and group; filter the 4 groups; Q1 2026 duplicates removed.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q3: 88 (ISE Admins 3, Cisco Net Admins 44, ISEAdmin 36, F5 5). 2026 Q1: 61 (ISE Admins 3, Cisco Net Admins 29, ISEAdmin 24, F5 5).</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Reconcile to Active Directory</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>AD extract 11/25/2025 (Q3_2025 tabs 1-4) and 05/15/2026 (Q1 2026 tabs 1-4)</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>AD members vs certified memberships.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2025 Q3: all approved members in AD except N584407 (removed after review); AD members not certified = X842395 (added 8/30/2025) and MIA25172 / MIA25175 ISEAdmin (added 9/10/2025) - added after the campaign launch, certified in 2026 Q1. 2026 Q1: all 58 AD members certified; 3 revoked memberships removed.</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Test the reviewer</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Decision Maker vs Identity / Manager / Assignee</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Person: line manager, not the holder; service account: owner.</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Both samples: managers / owners; no self-review.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Test the decision</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Decision, Decision Date, SignOff Date</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Every membership decided and signed off.</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: 88/88 (8/6-8/28/2025). 2026 Q1: 61/61 (4/10-4/30/2026).</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Obtain identity and account status</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>IAMS fields in the certifications; AD extracts</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Status at the decision date.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: 7 approved identities with IAMS termination date 12/31/2024 (MIA25103-06, MIA25249-51), MIA25103 disabled in AD with last logon 10/15/2023. 2026 Q1: 9 approved accounts disabled in AD since 4/2-4/3/2026; 8 IAMS terminated identities.</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Assess appropriateness</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Steps 11 and prior decisions</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Fail if approved while inactive / disabled (E1), terminated / expired (E2) or re-granted after revocation without request (E3).</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: 14 memberships (Cisco Net Admins 7, ISEAdmin 7). 2026 Q1: 30 memberships (Cisco Net Admins 16, ISEAdmin 14).</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>A5</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>STEP 5 - VALIDATE CONTROL RESULTS</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Step 13; Sample of 1 Exhibits B4 / B5</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Revoked access removed by PAM/IAM within SLA after the review and consistent with the decision.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2025 Q3: 33 revoked 8/28/2025, removed 9/2-9/8/2025 (Netwrix) - within 30 business days and matching the decisions; 6 memberships (X453396 x2, MIA25142 x2, MIA25172, MIA25175) were members again on 11/25/2025 - removal not sustained. 2026 Q1: N596764 x2 removed 4/24/2026, MIAYPER 4/17/2026 - within SLA, absent from AD 05/15/2026.</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Fail (A6 - 2025 Q3)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Test revocations within SLA and their persistence</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Netwrix logs (Q3_2025 tabs 2-3; Q1 2026 tabs 2-4); AD extracts</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Removal within 30 business days and absent from the next AD extract.</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>2025 Q3: 33 memberships revoked 8/28/2025 and removed 9/2-9/8/2025 (within SLA), BUT 6 (X453396 x2, MIA25142 x2, MIA25172, MIA25175 in Cisco Net Admins / ISEAdmin) were members again in AD on 11/25/2025 - removal not sustained (E3). 2026 Q1: N596764 x2 removed 4/24/2026, MIAYPER removed 4/17/2026; none in AD 05/15/2026.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>A6</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Check report reliability</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>All sources</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Fields and reconciliations.</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Reports reconcile to AD. Observations: 2025 Q3 AD extract tags revoked members still present without comment; Q1 2026 export rows repeated 5x; IAMS termination date vs AD expiration inconsistent.</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>STEP 6 - VERIFY EXCEPTION HANDLING</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Tab 5; Evidence Status #2, #12</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Where revocations were late, reviews incomplete or reviewer authorization missing, verify the exception was documented and managed per procedure.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>No reviews were incomplete and no reviewer authorization issues were found. The exceptions found by testing (approved terminated / disabled accounts; 6 revoked memberships present again in AD) were not identified, documented or managed by the PAM / IAM team - no exception record, ticket or comment exists in the evidence (the 2025 Q3 AD extract shows the revoked members without comment).</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Fail (not evidenced)</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>STEP 7 - VERIFY ESCALATION AND REMEDIATION</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Tab 5; Evidence Status #2, #12</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Exceptions escalated; remediation documented, assigned and tracked to resolution.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>No escalation, remediation plan, owner or tracking was provided for the exceptions; the same accounts were approved again in the next review (2025 Q3 -&gt; 2026 Q1), showing they were not remediated within the period. Management response and issue / action driver required.</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Fail (not evidenced)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>STEP 8 - ASSESS RISK MITIGATION</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Tab 3 conclusion; WP2 CPA</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Does the review identify inappropriate access and drive timely revocation?</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Partially. The review is initiated, complete and performed by the right reviewers, and revocations that were raised were removed on time. However it did not identify terminated / disabled accounts in Cisco Network Administrators and ISEAdmin in either review, and removals were not sustained, so the risk of inappropriate privileged network access is not fully mitigated.</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Fail - Needs Improvement</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>STEP 9 - SUMMARIZE TESTING COVERAGE</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>This tab; WP2 C39</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Coverage of completeness / accuracy, scope, initiation, reviewer authorization, execution, revocation decisions, timeliness, exception management, escalation, risk mitigation.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Completeness &amp; accuracy: Pass (obs.). Scope: Pass (obs.). Initiation / frequency: Pass (obs. - 2025 Q4 missing). Reviewer authorization: Pass. Certification execution: Pass. Revocation decisions / appropriateness: Fail. Timeliness of removal: Pass within SLA, Fail on persistence (2025 Q3). Exception management: Fail (not evidenced). Escalation: Fail (not evidenced). Risk mitigation: Fail. Overall: 2 of 2 samples Fail - Needs Improvement.</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Fail - Needs Improvement</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Conclude</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Tab 3</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Group fails if any attribute fails; sample fails if any group fails.</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Sample 1 (2025 Q3): FAIL (Cisco Net Admins, ISEAdmin - A5, A6). Sample 2 (2026 Q1): FAIL (Cisco Net Admins, ISEAdmin - A5). ISE Admins and F5FullAdmin pass in both. 2 of 2 samples fail -&gt; control performance Needs Improvement.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
@@ -1426,45 +1803,45 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Sample ID</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Quarterly PAM Access Certification (sample)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Privileged Network AD Group</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>A2 Completeness - members (users / service accounts) certified
-A3 Reviewer - manager / owner</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>A4 Decision &amp; approvers
-A5 Appropriateness of approved access</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>A1 Frequency
-A6 Revocations within SLA</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Steps 2-3: A2 Completeness - members (users / service accounts) certified
+Step 4: A3 Reviewer - manager / owner</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Step 4: A4 Decision &amp; approvers
+Step 4: A5 Appropriateness (revocations identified)</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Step 4: A1 Frequency / initiation
+Step 5: A6 Revocations within SLA</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Supporting evidence</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>Control Sample Assessment Result (Pass/Fail)</t>
         </is>
@@ -1512,7 +1889,7 @@
           <t>BSI.IT.27.C7.02 Q3_2025.xlsx tab 1_Cisco ISE Administrators; AD extract 11/25/2025</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1560,7 +1937,7 @@
           <t>BSI.IT.27.C7.02 Q3_2025.xlsx tab 2_Cisco Network Administrators; AD extract 11/25/2025</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1608,7 +1985,7 @@
           <t>BSI.IT.27.C7.02 Q3_2025.xlsx tab 3_ISEAdmin; AD extract 11/25/2025</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1656,7 +2033,7 @@
           <t>BSI.IT.27.C7.02 Q3_2025.xlsx tab 4_F5FullAdmin; AD extract 11/25/2025</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1704,7 +2081,7 @@
           <t>BSI.IT.27.C7.02 Q1 2026 Cert.xlsx tab 1.Cisco ISE Administrators; AD extract 05/15/2026</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1752,7 +2129,7 @@
           <t>BSI.IT.27.C7.02 Q1 2026 Cert.xlsx tab 2.Cisco Network Administrators; AD extract 05/15/2026</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1800,7 +2177,7 @@
           <t>BSI.IT.27.C7.02 Q1 2026 Cert.xlsx tab 3.ISEAdmin; AD extract 05/15/2026</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1848,7 +2225,7 @@
           <t>BSI.IT.27.C7.02 Q1 2026 Cert.xlsx tab 4.F5FullAdmin; AD extract 05/15/2026</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1894,7 +2271,7 @@
           <t>Frequency (at least semiannual) &amp; initiation</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Pass (observation)</t>
         </is>
@@ -1916,7 +2293,7 @@
           <t>Completeness - users / administrators and service accounts</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1938,7 +2315,7 @@
           <t>Reviewer - manager / owner</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1960,7 +2337,7 @@
           <t>Decision &amp; approvers</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1982,7 +2359,7 @@
           <t>Appropriateness of approved access</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -2004,7 +2381,7 @@
           <t>Revocations within SLA</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -2026,7 +2403,7 @@
           <t>Information reliability</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Observation</t>
         </is>
@@ -2038,7 +2415,7 @@
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Overall (period 07/01/2025 - 06/30/2026): 2 of 2 samples FAIL - CISCO Network Administrators and ISEAdmin (A5 in both samples; A6 in 2025 Q3). Control performance: Needs Improvement.</t>
         </is>
@@ -2299,17 +2676,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2319,7 +2696,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="W4" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2412,17 +2789,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2432,7 +2809,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2525,17 +2902,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U6" s="6" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2545,7 +2922,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W6" s="6" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2638,17 +3015,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U7" s="6" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2658,7 +3035,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W7" s="6" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2751,17 +3128,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U8" s="6" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2771,7 +3148,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W8" s="6" t="inlineStr">
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2864,17 +3241,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U9" s="6" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2884,7 +3261,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W9" s="6" t="inlineStr">
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2977,17 +3354,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U10" s="6" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2997,7 +3374,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W10" s="6" t="inlineStr">
+      <c r="W10" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3090,17 +3467,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3110,7 +3487,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W11" s="6" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3203,17 +3580,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T12" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U12" s="6" t="inlineStr">
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3223,7 +3600,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W12" s="6" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3316,17 +3693,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U13" s="6" t="inlineStr">
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3336,7 +3713,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W13" s="6" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3429,17 +3806,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3449,7 +3826,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W14" s="6" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3542,17 +3919,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U15" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 11/25/2025), last logon 10/15/2023 - no use since before the review; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -3562,7 +3939,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -3655,17 +4032,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U16" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -3675,7 +4052,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -3768,17 +4145,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T17" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U17" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -3788,7 +4165,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -3881,17 +4258,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T18" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U18" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -3901,7 +4278,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -3994,27 +4371,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
         <is>
           <t>FAIL - removal not sustained: revoked 8/28/2025, removed 09/02/2025 (Netwrix) but member again in AD 11/25/2025 (E3)</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4107,27 +4484,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
         <is>
           <t>FAIL - removal not sustained: revoked 8/28/2025, removed 09/02/2025 (Netwrix) but member again in AD 11/25/2025 (E3)</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4220,27 +4597,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W21" s="6" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4333,27 +4710,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
         <is>
           <t>FAIL - removal not sustained: revoked 8/28/2025, removed 09/08/2025 (Netwrix) but member again in AD 11/25/2025 (E3)</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4446,17 +4823,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U23" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -4466,7 +4843,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4559,17 +4936,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T24" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U24" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -4579,7 +4956,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4672,17 +5049,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T25" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U25" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -4692,7 +5069,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4785,17 +5162,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T26" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U26" s="6" t="inlineStr">
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4805,7 +5182,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W26" s="6" t="inlineStr">
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4898,17 +5275,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T27" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U27" s="6" t="inlineStr">
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4918,7 +5295,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W27" s="6" t="inlineStr">
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5011,17 +5388,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T28" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U28" s="6" t="inlineStr">
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5031,7 +5408,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W28" s="6" t="inlineStr">
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5124,17 +5501,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5144,7 +5521,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W29" s="6" t="inlineStr">
+      <c r="W29" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5237,27 +5614,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S30" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T30" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V30" s="6" t="inlineStr">
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W30" s="6" t="inlineStr">
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5350,27 +5727,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T31" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W31" s="6" t="inlineStr">
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5463,27 +5840,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T32" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W32" s="6" t="inlineStr">
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5576,27 +5953,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T33" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W33" s="6" t="inlineStr">
+      <c r="W33" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5689,27 +6066,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T34" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V34" s="6" t="inlineStr">
+      <c r="S34" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W34" s="6" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5802,27 +6179,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T35" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W35" s="6" t="inlineStr">
+      <c r="W35" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5915,27 +6292,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T36" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W36" s="6" t="inlineStr">
+      <c r="W36" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6028,27 +6405,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T37" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U37" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V37" s="6" t="inlineStr">
+      <c r="S37" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W37" s="6" t="inlineStr">
+      <c r="W37" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6141,27 +6518,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S38" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T38" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U38" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V38" s="6" t="inlineStr">
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W38" s="6" t="inlineStr">
+      <c r="W38" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6254,27 +6631,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T39" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U39" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V39" s="6" t="inlineStr">
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W39" s="6" t="inlineStr">
+      <c r="W39" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6367,27 +6744,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S40" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T40" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U40" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V40" s="6" t="inlineStr">
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W40" s="6" t="inlineStr">
+      <c r="W40" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6480,27 +6857,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S41" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T41" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U41" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V41" s="6" t="inlineStr">
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W41" s="6" t="inlineStr">
+      <c r="W41" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6593,27 +6970,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S42" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T42" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U42" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V42" s="6" t="inlineStr">
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W42" s="6" t="inlineStr">
+      <c r="W42" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6706,27 +7083,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S43" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T43" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U43" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
+      <c r="S43" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
         <is>
           <t>FAIL - removal not sustained: revoked 8/28/2025, removed 09/08/2025 (Netwrix) but member again in AD 11/25/2025 (E3)</t>
         </is>
       </c>
-      <c r="W43" s="8" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -6819,17 +7196,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S44" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T44" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U44" s="6" t="inlineStr">
+      <c r="S44" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6839,7 +7216,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W44" s="6" t="inlineStr">
+      <c r="W44" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6932,17 +7309,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S45" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T45" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U45" s="6" t="inlineStr">
+      <c r="S45" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6952,7 +7329,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W45" s="6" t="inlineStr">
+      <c r="W45" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7045,17 +7422,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S46" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T46" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U46" s="6" t="inlineStr">
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7065,7 +7442,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W46" s="6" t="inlineStr">
+      <c r="W46" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7158,17 +7535,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S47" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T47" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U47" s="6" t="inlineStr">
+      <c r="S47" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7178,7 +7555,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W47" s="6" t="inlineStr">
+      <c r="W47" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7271,17 +7648,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T48" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U48" s="6" t="inlineStr">
+      <c r="S48" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7291,7 +7668,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W48" s="6" t="inlineStr">
+      <c r="W48" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7384,17 +7761,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S49" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T49" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U49" s="6" t="inlineStr">
+      <c r="S49" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7404,7 +7781,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W49" s="6" t="inlineStr">
+      <c r="W49" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7497,17 +7874,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S50" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T50" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U50" s="6" t="inlineStr">
+      <c r="S50" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7517,7 +7894,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W50" s="6" t="inlineStr">
+      <c r="W50" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7610,17 +7987,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S51" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T51" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U51" s="6" t="inlineStr">
+      <c r="S51" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7630,7 +8007,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W51" s="6" t="inlineStr">
+      <c r="W51" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7723,17 +8100,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S52" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T52" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U52" s="6" t="inlineStr">
+      <c r="S52" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7743,7 +8120,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W52" s="6" t="inlineStr">
+      <c r="W52" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7836,17 +8213,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S53" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T53" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="S53" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U53" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 11/25/2025), last logon 10/15/2023 - no use since before the review; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -7856,7 +8233,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W53" s="8" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -7949,17 +8326,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S54" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T54" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="S54" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U54" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -7969,7 +8346,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W54" s="8" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8062,17 +8439,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S55" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T55" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="S55" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U55" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -8082,7 +8459,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W55" s="8" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8175,17 +8552,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S56" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T56" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="S56" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U56" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -8195,7 +8572,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W56" s="8" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8288,27 +8665,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S57" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T57" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U57" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
+      <c r="S57" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V57" s="11" t="inlineStr">
         <is>
           <t>FAIL - removal not sustained: revoked 8/28/2025, removed 09/02/2025 (Netwrix) but member again in AD 11/25/2025 (E3)</t>
         </is>
       </c>
-      <c r="W57" s="8" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8401,17 +8778,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S58" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T58" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="S58" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U58" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -8421,7 +8798,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W58" s="8" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8514,17 +8891,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S59" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T59" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
+      <c r="S59" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U59" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -8534,7 +8911,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W59" s="8" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8627,17 +9004,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S60" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T60" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
+      <c r="S60" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U60" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -8647,7 +9024,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W60" s="8" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8740,17 +9117,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T61" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U61" s="6" t="inlineStr">
+      <c r="S61" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8760,7 +9137,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W61" s="6" t="inlineStr">
+      <c r="W61" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8853,17 +9230,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S62" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T62" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U62" s="6" t="inlineStr">
+      <c r="S62" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8873,7 +9250,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W62" s="6" t="inlineStr">
+      <c r="W62" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8966,17 +9343,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S63" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T63" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U63" s="6" t="inlineStr">
+      <c r="S63" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8986,7 +9363,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W63" s="6" t="inlineStr">
+      <c r="W63" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9079,17 +9456,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S64" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T64" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U64" s="6" t="inlineStr">
+      <c r="S64" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9099,7 +9476,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W64" s="6" t="inlineStr">
+      <c r="W64" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9192,17 +9569,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T65" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U65" s="6" t="inlineStr">
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9212,7 +9589,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W65" s="6" t="inlineStr">
+      <c r="W65" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9305,27 +9682,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S66" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T66" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U66" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V66" s="6" t="inlineStr">
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U66" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V66" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W66" s="6" t="inlineStr">
+      <c r="W66" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9418,27 +9795,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S67" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T67" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U67" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V67" s="6" t="inlineStr">
+      <c r="S67" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V67" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W67" s="6" t="inlineStr">
+      <c r="W67" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9531,27 +9908,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T68" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U68" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V68" s="6" t="inlineStr">
+      <c r="S68" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U68" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V68" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W68" s="6" t="inlineStr">
+      <c r="W68" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9644,27 +10021,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S69" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T69" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U69" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V69" s="6" t="inlineStr">
+      <c r="S69" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U69" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V69" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W69" s="6" t="inlineStr">
+      <c r="W69" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9757,27 +10134,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S70" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T70" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U70" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V70" s="6" t="inlineStr">
+      <c r="S70" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V70" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W70" s="6" t="inlineStr">
+      <c r="W70" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9870,27 +10247,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T71" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U71" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V71" s="6" t="inlineStr">
+      <c r="S71" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U71" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V71" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W71" s="6" t="inlineStr">
+      <c r="W71" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9983,27 +10360,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T72" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U72" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V72" s="6" t="inlineStr">
+      <c r="S72" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V72" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W72" s="6" t="inlineStr">
+      <c r="W72" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10096,27 +10473,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S73" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T73" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V73" s="6" t="inlineStr">
+      <c r="S73" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U73" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V73" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W73" s="6" t="inlineStr">
+      <c r="W73" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10209,27 +10586,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S74" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T74" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U74" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V74" s="6" t="inlineStr">
+      <c r="S74" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U74" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V74" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W74" s="6" t="inlineStr">
+      <c r="W74" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10322,27 +10699,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S75" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T75" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U75" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V75" s="6" t="inlineStr">
+      <c r="S75" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U75" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V75" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W75" s="6" t="inlineStr">
+      <c r="W75" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10435,27 +10812,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T76" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U76" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V76" s="6" t="inlineStr">
+      <c r="S76" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V76" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W76" s="6" t="inlineStr">
+      <c r="W76" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10548,27 +10925,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S77" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T77" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U77" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V77" s="6" t="inlineStr">
+      <c r="S77" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U77" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V77" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W77" s="6" t="inlineStr">
+      <c r="W77" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10661,27 +11038,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S78" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T78" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U78" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V78" s="6" t="inlineStr">
+      <c r="S78" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U78" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V78" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 8/28/2025, removed 09/02-09/08/2025 (Netwrix); not in AD 11/25/2025</t>
         </is>
       </c>
-      <c r="W78" s="6" t="inlineStr">
+      <c r="W78" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10774,27 +11151,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S79" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T79" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U79" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V79" s="8" t="inlineStr">
+      <c r="S79" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U79" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V79" s="11" t="inlineStr">
         <is>
           <t>FAIL - removal not sustained: revoked 8/28/2025, removed 09/08/2025 (Netwrix) but member again in AD 11/25/2025 (E3)</t>
         </is>
       </c>
-      <c r="W79" s="8" t="inlineStr">
+      <c r="W79" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -10887,17 +11264,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U80" s="6" t="inlineStr">
+      <c r="S80" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U80" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10907,7 +11284,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W80" s="6" t="inlineStr">
+      <c r="W80" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11000,17 +11377,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T81" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U81" s="6" t="inlineStr">
+      <c r="S81" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U81" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11020,7 +11397,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W81" s="6" t="inlineStr">
+      <c r="W81" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11113,17 +11490,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T82" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U82" s="6" t="inlineStr">
+      <c r="S82" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U82" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11133,7 +11510,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W82" s="6" t="inlineStr">
+      <c r="W82" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11226,17 +11603,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T83" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U83" s="6" t="inlineStr">
+      <c r="S83" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U83" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11246,7 +11623,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W83" s="6" t="inlineStr">
+      <c r="W83" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11339,17 +11716,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S84" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T84" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U84" s="6" t="inlineStr">
+      <c r="S84" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U84" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11359,7 +11736,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W84" s="6" t="inlineStr">
+      <c r="W84" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11452,17 +11829,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S85" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T85" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U85" s="6" t="inlineStr">
+      <c r="S85" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11472,7 +11849,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W85" s="6" t="inlineStr">
+      <c r="W85" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11565,17 +11942,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T86" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U86" s="6" t="inlineStr">
+      <c r="S86" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U86" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11585,7 +11962,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W86" s="6" t="inlineStr">
+      <c r="W86" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11678,17 +12055,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S87" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T87" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U87" s="6" t="inlineStr">
+      <c r="S87" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11698,7 +12075,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W87" s="6" t="inlineStr">
+      <c r="W87" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11791,17 +12168,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S88" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T88" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U88" s="6" t="inlineStr">
+      <c r="S88" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11811,7 +12188,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W88" s="6" t="inlineStr">
+      <c r="W88" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11904,17 +12281,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S89" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T89" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U89" s="6" t="inlineStr">
+      <c r="S89" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -11924,7 +12301,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W89" s="6" t="inlineStr">
+      <c r="W89" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12017,17 +12394,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S90" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T90" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U90" s="6" t="inlineStr">
+      <c r="S90" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U90" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12037,7 +12414,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W90" s="6" t="inlineStr">
+      <c r="W90" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12130,17 +12507,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S91" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T91" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U91" s="6" t="inlineStr">
+      <c r="S91" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12150,7 +12527,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W91" s="6" t="inlineStr">
+      <c r="W91" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12243,17 +12620,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S92" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T92" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U92" s="6" t="inlineStr">
+      <c r="S92" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T92" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U92" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12263,7 +12640,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W92" s="6" t="inlineStr">
+      <c r="W92" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12356,17 +12733,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S93" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T93" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U93" s="6" t="inlineStr">
+      <c r="S93" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T93" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U93" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12376,7 +12753,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W93" s="6" t="inlineStr">
+      <c r="W93" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12469,17 +12846,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S94" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T94" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U94" s="6" t="inlineStr">
+      <c r="S94" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T94" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U94" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12489,7 +12866,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W94" s="6" t="inlineStr">
+      <c r="W94" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12582,17 +12959,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S95" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T95" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U95" s="6" t="inlineStr">
+      <c r="S95" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T95" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U95" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12602,7 +12979,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W95" s="6" t="inlineStr">
+      <c r="W95" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12695,17 +13072,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S96" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T96" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U96" s="6" t="inlineStr">
+      <c r="S96" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T96" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U96" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12715,7 +13092,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W96" s="6" t="inlineStr">
+      <c r="W96" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12808,17 +13185,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S97" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T97" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U97" s="6" t="inlineStr">
+      <c r="S97" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T97" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U97" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12828,7 +13205,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W97" s="6" t="inlineStr">
+      <c r="W97" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12921,17 +13298,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S98" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T98" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U98" s="6" t="inlineStr">
+      <c r="S98" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T98" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U98" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12941,7 +13318,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W98" s="6" t="inlineStr">
+      <c r="W98" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13034,17 +13411,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S99" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T99" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U99" s="6" t="inlineStr">
+      <c r="S99" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T99" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U99" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13054,7 +13431,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W99" s="6" t="inlineStr">
+      <c r="W99" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13147,17 +13524,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S100" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T100" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U100" s="6" t="inlineStr">
+      <c r="S100" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T100" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U100" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13167,7 +13544,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W100" s="6" t="inlineStr">
+      <c r="W100" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13260,17 +13637,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S101" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T101" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U101" s="6" t="inlineStr">
+      <c r="S101" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T101" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U101" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13280,7 +13657,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W101" s="6" t="inlineStr">
+      <c r="W101" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13373,17 +13750,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S102" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T102" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U102" s="6" t="inlineStr">
+      <c r="S102" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T102" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U102" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13393,7 +13770,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W102" s="6" t="inlineStr">
+      <c r="W102" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13486,17 +13863,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S103" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T103" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U103" s="8" t="inlineStr">
+      <c r="S103" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T103" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U103" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -13506,7 +13883,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W103" s="8" t="inlineStr">
+      <c r="W103" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -13599,17 +13976,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S104" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T104" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U104" s="8" t="inlineStr">
+      <c r="S104" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T104" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U104" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -13619,7 +13996,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W104" s="8" t="inlineStr">
+      <c r="W104" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -13712,17 +14089,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S105" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T105" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U105" s="8" t="inlineStr">
+      <c r="S105" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T105" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U105" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -13732,7 +14109,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W105" s="8" t="inlineStr">
+      <c r="W105" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -13825,17 +14202,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S106" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T106" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U106" s="8" t="inlineStr">
+      <c r="S106" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T106" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U106" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -13845,7 +14222,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W106" s="8" t="inlineStr">
+      <c r="W106" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -13938,17 +14315,17 @@
           <t>Revoked</t>
         </is>
       </c>
-      <c r="S107" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T107" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U107" s="8" t="inlineStr">
+      <c r="S107" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T107" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U107" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024; E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
         </is>
@@ -13958,7 +14335,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W107" s="8" t="inlineStr">
+      <c r="W107" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14051,17 +14428,17 @@
           <t>Revoked</t>
         </is>
       </c>
-      <c r="S108" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T108" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U108" s="8" t="inlineStr">
+      <c r="S108" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T108" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U108" s="11" t="inlineStr">
         <is>
           <t>Fail - E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
         </is>
@@ -14071,7 +14448,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W108" s="8" t="inlineStr">
+      <c r="W108" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14164,17 +14541,17 @@
           <t>Revoked</t>
         </is>
       </c>
-      <c r="S109" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T109" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U109" s="8" t="inlineStr">
+      <c r="S109" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T109" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U109" s="11" t="inlineStr">
         <is>
           <t>Fail - E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
         </is>
@@ -14184,7 +14561,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W109" s="8" t="inlineStr">
+      <c r="W109" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14277,17 +14654,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S110" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T110" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U110" s="8" t="inlineStr">
+      <c r="S110" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T110" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U110" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -14297,7 +14674,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W110" s="8" t="inlineStr">
+      <c r="W110" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14390,17 +14767,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S111" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T111" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U111" s="8" t="inlineStr">
+      <c r="S111" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T111" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U111" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -14410,7 +14787,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W111" s="8" t="inlineStr">
+      <c r="W111" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14503,17 +14880,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S112" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T112" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U112" s="8" t="inlineStr">
+      <c r="S112" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T112" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U112" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -14523,7 +14900,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W112" s="8" t="inlineStr">
+      <c r="W112" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14616,17 +14993,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S113" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T113" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U113" s="6" t="inlineStr">
+      <c r="S113" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T113" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U113" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14636,7 +15013,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W113" s="6" t="inlineStr">
+      <c r="W113" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14729,27 +15106,27 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S114" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T114" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U114" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V114" s="6" t="inlineStr">
+      <c r="S114" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T114" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U114" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V114" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 04/24/2026, removed 04/24/2026 (Netwrix); not in AD 05/15/2026</t>
         </is>
       </c>
-      <c r="W114" s="6" t="inlineStr">
+      <c r="W114" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14842,17 +15219,17 @@
           <t>Revoked</t>
         </is>
       </c>
-      <c r="S115" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T115" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U115" s="8" t="inlineStr">
+      <c r="S115" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T115" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U115" s="11" t="inlineStr">
         <is>
           <t>Fail - E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
         </is>
@@ -14862,7 +15239,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W115" s="8" t="inlineStr">
+      <c r="W115" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14955,17 +15332,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S116" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T116" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U116" s="6" t="inlineStr">
+      <c r="S116" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T116" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U116" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14975,7 +15352,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W116" s="6" t="inlineStr">
+      <c r="W116" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15068,17 +15445,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S117" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T117" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U117" s="8" t="inlineStr">
+      <c r="S117" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T117" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U117" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -15088,7 +15465,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W117" s="8" t="inlineStr">
+      <c r="W117" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -15181,17 +15558,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S118" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T118" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U118" s="8" t="inlineStr">
+      <c r="S118" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T118" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U118" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -15201,7 +15578,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W118" s="8" t="inlineStr">
+      <c r="W118" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -15294,17 +15671,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S119" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T119" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U119" s="8" t="inlineStr">
+      <c r="S119" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T119" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U119" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -15314,7 +15691,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W119" s="8" t="inlineStr">
+      <c r="W119" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -15407,17 +15784,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S120" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T120" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U120" s="8" t="inlineStr">
+      <c r="S120" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T120" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U120" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -15427,7 +15804,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W120" s="8" t="inlineStr">
+      <c r="W120" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -15520,17 +15897,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S121" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T121" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U121" s="8" t="inlineStr">
+      <c r="S121" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T121" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U121" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -15540,7 +15917,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W121" s="8" t="inlineStr">
+      <c r="W121" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -15633,17 +16010,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S122" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T122" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U122" s="6" t="inlineStr">
+      <c r="S122" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T122" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U122" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15653,7 +16030,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W122" s="6" t="inlineStr">
+      <c r="W122" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15746,17 +16123,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S123" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T123" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U123" s="6" t="inlineStr">
+      <c r="S123" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T123" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U123" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15766,7 +16143,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W123" s="6" t="inlineStr">
+      <c r="W123" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15859,17 +16236,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S124" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T124" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U124" s="6" t="inlineStr">
+      <c r="S124" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T124" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U124" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15879,7 +16256,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W124" s="6" t="inlineStr">
+      <c r="W124" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15972,17 +16349,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S125" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T125" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U125" s="6" t="inlineStr">
+      <c r="S125" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T125" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U125" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15992,7 +16369,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W125" s="6" t="inlineStr">
+      <c r="W125" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16085,17 +16462,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S126" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T126" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U126" s="8" t="inlineStr">
+      <c r="S126" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T126" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U126" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -16105,7 +16482,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W126" s="8" t="inlineStr">
+      <c r="W126" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16198,17 +16575,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S127" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T127" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U127" s="8" t="inlineStr">
+      <c r="S127" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T127" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U127" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -16218,7 +16595,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W127" s="8" t="inlineStr">
+      <c r="W127" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16311,17 +16688,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S128" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T128" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U128" s="8" t="inlineStr">
+      <c r="S128" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T128" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U128" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -16331,7 +16708,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W128" s="8" t="inlineStr">
+      <c r="W128" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16424,17 +16801,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S129" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T129" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U129" s="8" t="inlineStr">
+      <c r="S129" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T129" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U129" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -16444,7 +16821,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W129" s="8" t="inlineStr">
+      <c r="W129" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16537,17 +16914,17 @@
           <t>Revoked</t>
         </is>
       </c>
-      <c r="S130" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T130" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U130" s="8" t="inlineStr">
+      <c r="S130" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T130" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U130" s="11" t="inlineStr">
         <is>
           <t>Fail - E2 IAMS Termination Date 12/31/2024; E3 revoked 2025 Q3 (removed 09/02/2025 per Netwrix) - re-granted without approved request</t>
         </is>
@@ -16557,7 +16934,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W130" s="8" t="inlineStr">
+      <c r="W130" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16650,17 +17027,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S131" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T131" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U131" s="6" t="inlineStr">
+      <c r="S131" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T131" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U131" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16670,7 +17047,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W131" s="6" t="inlineStr">
+      <c r="W131" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16763,17 +17140,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S132" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T132" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U132" s="6" t="inlineStr">
+      <c r="S132" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T132" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U132" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16783,7 +17160,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W132" s="6" t="inlineStr">
+      <c r="W132" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16876,17 +17253,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S133" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T133" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U133" s="8" t="inlineStr">
+      <c r="S133" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T133" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U133" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/02/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -16896,7 +17273,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W133" s="8" t="inlineStr">
+      <c r="W133" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16989,17 +17366,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S134" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T134" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U134" s="8" t="inlineStr">
+      <c r="S134" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T134" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U134" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -17009,7 +17386,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W134" s="8" t="inlineStr">
+      <c r="W134" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -17102,17 +17479,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S135" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T135" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U135" s="8" t="inlineStr">
+      <c r="S135" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T135" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U135" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision; E2 IAMS Termination Date 12/31/2024</t>
         </is>
@@ -17122,7 +17499,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W135" s="8" t="inlineStr">
+      <c r="W135" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -17215,17 +17592,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S136" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T136" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U136" s="6" t="inlineStr">
+      <c r="S136" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T136" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U136" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17235,7 +17612,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W136" s="6" t="inlineStr">
+      <c r="W136" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17328,17 +17705,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S137" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T137" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U137" s="6" t="inlineStr">
+      <c r="S137" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T137" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U137" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17348,7 +17725,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W137" s="6" t="inlineStr">
+      <c r="W137" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17441,27 +17818,27 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S138" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T138" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U138" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V138" s="6" t="inlineStr">
+      <c r="S138" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T138" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U138" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V138" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 04/24/2026, removed 04/24/2026 (Netwrix); not in AD 05/15/2026</t>
         </is>
       </c>
-      <c r="W138" s="6" t="inlineStr">
+      <c r="W138" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17554,17 +17931,17 @@
           <t>Revoked</t>
         </is>
       </c>
-      <c r="S139" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T139" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U139" s="8" t="inlineStr">
+      <c r="S139" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T139" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U139" s="11" t="inlineStr">
         <is>
           <t>Fail - E3 revoked 2025 Q3 (removed 09/08/2025 per Netwrix) - re-granted without approved request</t>
         </is>
@@ -17574,7 +17951,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W139" s="8" t="inlineStr">
+      <c r="W139" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -17667,17 +18044,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S140" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T140" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U140" s="6" t="inlineStr">
+      <c r="S140" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T140" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U140" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17687,7 +18064,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W140" s="6" t="inlineStr">
+      <c r="W140" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17780,17 +18157,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S141" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T141" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U141" s="8" t="inlineStr">
+      <c r="S141" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T141" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U141" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -17800,7 +18177,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W141" s="8" t="inlineStr">
+      <c r="W141" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -17893,17 +18270,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S142" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T142" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U142" s="8" t="inlineStr">
+      <c r="S142" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T142" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U142" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -17913,7 +18290,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W142" s="8" t="inlineStr">
+      <c r="W142" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -18006,17 +18383,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S143" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T143" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U143" s="8" t="inlineStr">
+      <c r="S143" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T143" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U143" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -18026,7 +18403,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W143" s="8" t="inlineStr">
+      <c r="W143" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -18119,17 +18496,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S144" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T144" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U144" s="8" t="inlineStr">
+      <c r="S144" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T144" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U144" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -18139,7 +18516,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W144" s="8" t="inlineStr">
+      <c r="W144" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -18232,17 +18609,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S145" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T145" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U145" s="8" t="inlineStr">
+      <c r="S145" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T145" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U145" s="11" t="inlineStr">
         <is>
           <t>Fail - E1 AD account disabled (AD 05/15/2026, last changed 04/03/2026) before the decision</t>
         </is>
@@ -18252,7 +18629,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W145" s="8" t="inlineStr">
+      <c r="W145" s="11" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -18345,17 +18722,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S146" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T146" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U146" s="6" t="inlineStr">
+      <c r="S146" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T146" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U146" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18365,7 +18742,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W146" s="6" t="inlineStr">
+      <c r="W146" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18458,17 +18835,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S147" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T147" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U147" s="6" t="inlineStr">
+      <c r="S147" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T147" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U147" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18478,7 +18855,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W147" s="6" t="inlineStr">
+      <c r="W147" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18571,17 +18948,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S148" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T148" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U148" s="6" t="inlineStr">
+      <c r="S148" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T148" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U148" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18591,7 +18968,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W148" s="6" t="inlineStr">
+      <c r="W148" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18684,17 +19061,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S149" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T149" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U149" s="6" t="inlineStr">
+      <c r="S149" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T149" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U149" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18704,7 +19081,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W149" s="6" t="inlineStr">
+      <c r="W149" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18797,17 +19174,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S150" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T150" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U150" s="6" t="inlineStr">
+      <c r="S150" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T150" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U150" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18817,7 +19194,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W150" s="6" t="inlineStr">
+      <c r="W150" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18910,17 +19287,17 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S151" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T151" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U151" s="6" t="inlineStr">
+      <c r="S151" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T151" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U151" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18930,7 +19307,7 @@
           <t>N/A - Approved</t>
         </is>
       </c>
-      <c r="W151" s="6" t="inlineStr">
+      <c r="W151" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -19023,27 +19400,27 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="S152" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="T152" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="U152" s="6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="V152" s="6" t="inlineStr">
+      <c r="S152" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="T152" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U152" s="8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="V152" s="8" t="inlineStr">
         <is>
           <t>Pass - revoked 04/16/2026, removed 04/17/2026 (Netwrix); not in AD 05/15/2026</t>
         </is>
       </c>
-      <c r="W152" s="6" t="inlineStr">
+      <c r="W152" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -19827,7 +20204,7 @@
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Totals: 16 accounts. 2025 Q3: 20 memberships (A5 14, A6 6); 2026 Q1: 30 memberships (A5 30). E1 = IAMS inactive / AD disabled; E2 = IAMS terminated / AD expired; E3 = revoked access present again / re-granted without approved request.</t>
         </is>
@@ -19995,71 +20372,71 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>BSI.IT.27.C7.02 Q3_2025.xlsx</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 02 Evidence 07.2025-06.2026</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>2025 Q3 - SAMPLE 1 (H2 2025)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>3743 KB</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>2025 Q3 SOX Manager / Owner certification (launched 8/1/2025, decisions 8/6-8/28/2025), AD extract 11/25/2025, Netwrix revocation logs 9/2-9/8/2025</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>9df232d76e15d4e56a5f55da1d84aa4a</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>BSI.IT.27.C7.02 Q1 2026 Cert.xlsx</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>BSI.IT.27.C7 Network Device Admin Accoun / BSI.IT.27.C7 Final 07.2025-06.2026 / 02 Evidence 07.2025-06.2026</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>2026 Q1 - SAMPLE 2 (H1 2026)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>3063 KB</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>2026 Q1 SOX Manager / Owner certification (launched 4/9/2026, decisions 4/10-4/30/2026), AD extract 05/15/2026, Netwrix revocation logs 4/16-4/24/2026</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>8d338a2151c9c28eff23af70e6583695</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Only evidence within the testing period 07/01/2025 - 06/30/2026 is used. Files received 10/01/2026 that fall outside the period (2025 Q1, 2025 Q2, 2026 Q2 certifications) are not relied on and are not in the final folder.</t>
         </is>
@@ -20155,7 +20532,7 @@
           <t>IAM / PAM team</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20190,7 +20567,7 @@
           <t>Control owner</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20225,7 +20602,7 @@
           <t>HR / Vendor mgmt</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20260,7 +20637,7 @@
           <t>HR / IAM</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20295,7 +20672,7 @@
           <t>PAM / IAM; InfoSec (Netwrix)</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20330,7 +20707,7 @@
           <t>IT Ops / InfoSec</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
@@ -20365,7 +20742,7 @@
           <t>IAM / PAM</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
@@ -20400,7 +20777,7 @@
           <t>InfoSec</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
@@ -20435,7 +20812,7 @@
           <t>IAM</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20470,7 +20847,7 @@
           <t>Policy administration</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20505,7 +20882,7 @@
           <t>PAM / IAM; control owner</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20540,7 +20917,7 @@
           <t>InfoSec / control owner</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -20557,7 +20934,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Essential to close the testing: #1 (2025 Q4) and #2 (management response). #3-#5 decide whether any exception can be cleared.</t>
         </is>
@@ -20652,7 +21029,7 @@
           <t>Tabs 6, 7; 02 Evidence; 01 Policies</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Pass (observation)</t>
         </is>
@@ -20682,7 +21059,7 @@
           <t>Step 8; Sample of 1 Exhibit C1; tab 4</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Pass (observation)</t>
         </is>
@@ -20712,7 +21089,7 @@
           <t>Steps 1, 7; tab 3</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Pass (observation)</t>
         </is>
@@ -20742,7 +21119,7 @@
           <t>Steps 6, 9-12; tab 3; tab 5</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Fail (A5)</t>
         </is>
@@ -20772,7 +21149,7 @@
           <t>Step 13; Sample of 1 Exhibits B4 / B5</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Fail (A6 - 2025 Q3)</t>
         </is>
@@ -20802,7 +21179,7 @@
           <t>Tab 5; Evidence Status #2, #12</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Fail (not evidenced)</t>
         </is>
@@ -20832,7 +21209,7 @@
           <t>Tab 5; Evidence Status #2, #12</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Fail (not evidenced)</t>
         </is>
@@ -20862,7 +21239,7 @@
           <t>Tab 3 conclusion; WP2 CPA</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Fail - Needs Improvement</t>
         </is>
@@ -20892,7 +21269,7 @@
           <t>This tab; WP2 C39</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Fail - Needs Improvement</t>
         </is>
